--- a/115 僑生B班.xlsx
+++ b/115 僑生B班.xlsx
@@ -1,17 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE362885-9E43-4FBE-B91C-A1C01EE07AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12285"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
     <sheet name="工作表2" sheetId="2" r:id="rId2"/>
     <sheet name="工作表3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -20,17 +21,16 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>排名</t>
   </si>
@@ -155,13 +155,25 @@
   </si>
   <si>
     <t>英打比賽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>class0807</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中打網站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中文聽打</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -231,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -240,7 +252,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -259,9 +270,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -299,9 +310,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -336,7 +347,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -371,7 +382,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -544,13 +555,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:II37"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="5.625" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="5.625" style="4" customWidth="1"/>
     <col min="6" max="6" width="4.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5" bestFit="1" customWidth="1"/>
     <col min="15" max="19" width="5.75" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="6.875" bestFit="1" customWidth="1"/>
     <col min="22" max="29" width="4.875" bestFit="1" customWidth="1"/>
@@ -599,11 +611,11 @@
       <c r="E1" s="3"/>
       <c r="J1" s="2">
         <f>MIN(J3:J21)-1</f>
-        <v>-1</v>
+        <v>39</v>
       </c>
       <c r="K1" s="2">
         <f t="shared" ref="K1:BV1" si="0">MIN(K3:K21)-1</f>
-        <v>-1</v>
+        <v>39</v>
       </c>
       <c r="L1" s="2">
         <f t="shared" si="0"/>
@@ -1364,6 +1376,15 @@
       <c r="I2" s="4" t="s">
         <v>40</v>
       </c>
+      <c r="J2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="3" spans="1:195" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -1374,7 +1395,7 @@
       </c>
       <c r="C3" s="4">
         <f>SUM(H3:BR3)/63+60</f>
-        <v>60.634920634920633</v>
+        <v>62.38095238095238</v>
       </c>
       <c r="D3" s="4">
         <f>SUM(BS3:EH3)/(131-63)+60</f>
@@ -1386,14 +1407,26 @@
       </c>
       <c r="F3">
         <f>RANK(G3,$G$3:$G$36)</f>
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="G3">
         <f>SUM(H3:AAB3)</f>
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="H3">
         <v>40</v>
+      </c>
+      <c r="I3">
+        <v>10</v>
+      </c>
+      <c r="J3">
+        <v>40</v>
+      </c>
+      <c r="K3">
+        <v>40</v>
+      </c>
+      <c r="L3">
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:195" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -1405,7 +1438,7 @@
       </c>
       <c r="C4" s="4">
         <f t="shared" ref="C4:C22" si="3">SUM(H4:BR4)/63+60</f>
-        <v>60.634920634920633</v>
+        <v>63.142857142857146</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" ref="D4:D22" si="4">SUM(BS4:EH4)/(131-63)+60</f>
@@ -1417,13 +1450,25 @@
       </c>
       <c r="F4">
         <f t="shared" ref="F4:F36" si="6">RANK(G4,$G$3:$G$36)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G4">
         <f t="shared" ref="G4:G36" si="7">SUM(H4:AAB4)</f>
-        <v>40</v>
+        <v>198</v>
       </c>
       <c r="H4">
+        <v>40</v>
+      </c>
+      <c r="I4">
+        <v>38</v>
+      </c>
+      <c r="J4">
+        <v>40</v>
+      </c>
+      <c r="K4">
+        <v>40</v>
+      </c>
+      <c r="L4">
         <v>40</v>
       </c>
     </row>
@@ -1436,7 +1481,7 @@
       </c>
       <c r="C5" s="4">
         <f t="shared" si="3"/>
-        <v>60.634920634920633</v>
+        <v>62.746031746031747</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="4"/>
@@ -1448,14 +1493,26 @@
       </c>
       <c r="F5">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G5">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>173</v>
       </c>
       <c r="H5">
         <v>40</v>
+      </c>
+      <c r="I5">
+        <v>33</v>
+      </c>
+      <c r="J5">
+        <v>40</v>
+      </c>
+      <c r="K5">
+        <v>40</v>
+      </c>
+      <c r="L5">
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:195" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -1467,7 +1524,7 @@
       </c>
       <c r="C6" s="4">
         <f t="shared" si="3"/>
-        <v>60.634920634920633</v>
+        <v>63.015873015873012</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="4"/>
@@ -1479,13 +1536,25 @@
       </c>
       <c r="F6">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>190</v>
       </c>
       <c r="H6">
+        <v>40</v>
+      </c>
+      <c r="I6">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>40</v>
+      </c>
+      <c r="K6">
+        <v>40</v>
+      </c>
+      <c r="L6">
         <v>40</v>
       </c>
     </row>
@@ -1498,7 +1567,7 @@
       </c>
       <c r="C7" s="4">
         <f t="shared" si="3"/>
-        <v>60.634920634920633</v>
+        <v>62.698412698412696</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="4"/>
@@ -1510,13 +1579,25 @@
       </c>
       <c r="F7">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G7">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="H7">
+        <v>40</v>
+      </c>
+      <c r="I7">
+        <v>10</v>
+      </c>
+      <c r="J7">
+        <v>40</v>
+      </c>
+      <c r="K7">
+        <v>40</v>
+      </c>
+      <c r="L7">
         <v>40</v>
       </c>
     </row>
@@ -1529,7 +1610,7 @@
       </c>
       <c r="C8" s="4">
         <f t="shared" si="3"/>
-        <v>60.634920634920633</v>
+        <v>62.587301587301589</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="4"/>
@@ -1541,14 +1622,26 @@
       </c>
       <c r="F8">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="G8">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>163</v>
       </c>
       <c r="H8">
         <v>40</v>
+      </c>
+      <c r="I8">
+        <v>23</v>
+      </c>
+      <c r="J8">
+        <v>40</v>
+      </c>
+      <c r="K8">
+        <v>40</v>
+      </c>
+      <c r="L8">
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:195" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -1560,7 +1653,7 @@
       </c>
       <c r="C9" s="4">
         <f t="shared" si="3"/>
-        <v>60.634920634920633</v>
+        <v>62.571428571428569</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="4"/>
@@ -1572,14 +1665,26 @@
       </c>
       <c r="F9">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="G9">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>162</v>
       </c>
       <c r="H9">
         <v>40</v>
+      </c>
+      <c r="I9">
+        <v>22</v>
+      </c>
+      <c r="J9">
+        <v>40</v>
+      </c>
+      <c r="K9">
+        <v>40</v>
+      </c>
+      <c r="L9">
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:195" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -1591,7 +1696,7 @@
       </c>
       <c r="C10" s="4">
         <f t="shared" si="3"/>
-        <v>60.634920634920633</v>
+        <v>63.111111111111114</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="4"/>
@@ -1603,13 +1708,25 @@
       </c>
       <c r="F10">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G10">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>196</v>
       </c>
       <c r="H10">
+        <v>40</v>
+      </c>
+      <c r="I10">
+        <v>36</v>
+      </c>
+      <c r="J10">
+        <v>40</v>
+      </c>
+      <c r="K10">
+        <v>40</v>
+      </c>
+      <c r="L10">
         <v>40</v>
       </c>
     </row>
@@ -1622,7 +1739,7 @@
       </c>
       <c r="C11" s="4">
         <f t="shared" si="3"/>
-        <v>60.634920634920633</v>
+        <v>62.38095238095238</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="4"/>
@@ -1634,14 +1751,26 @@
       </c>
       <c r="F11">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="G11">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="H11">
         <v>40</v>
+      </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
+      <c r="J11">
+        <v>40</v>
+      </c>
+      <c r="K11">
+        <v>40</v>
+      </c>
+      <c r="L11">
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:195" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -1653,7 +1782,7 @@
       </c>
       <c r="C12" s="4">
         <f t="shared" si="3"/>
-        <v>60.634920634920633</v>
+        <v>63.095238095238095</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="4"/>
@@ -1665,17 +1794,29 @@
       </c>
       <c r="F12">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G12">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>195</v>
       </c>
       <c r="H12">
         <v>40</v>
       </c>
+      <c r="I12">
+        <v>35</v>
+      </c>
+      <c r="J12">
+        <v>40</v>
+      </c>
+      <c r="K12">
+        <v>40</v>
+      </c>
+      <c r="L12">
+        <v>40</v>
+      </c>
     </row>
-    <row r="13" spans="1:195" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:195" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1684,7 +1825,7 @@
       </c>
       <c r="C13" s="4">
         <f t="shared" si="3"/>
-        <v>60.634920634920633</v>
+        <v>62.38095238095238</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="4"/>
@@ -1696,14 +1837,26 @@
       </c>
       <c r="F13">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="G13">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="H13">
         <v>40</v>
+      </c>
+      <c r="I13">
+        <v>10</v>
+      </c>
+      <c r="J13">
+        <v>40</v>
+      </c>
+      <c r="K13">
+        <v>40</v>
+      </c>
+      <c r="L13">
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:195" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -1715,7 +1868,7 @@
       </c>
       <c r="C14" s="4">
         <f t="shared" si="3"/>
-        <v>60.634920634920633</v>
+        <v>62.952380952380949</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="4"/>
@@ -1727,13 +1880,25 @@
       </c>
       <c r="F14">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G14">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>186</v>
       </c>
       <c r="H14">
+        <v>40</v>
+      </c>
+      <c r="I14">
+        <v>26</v>
+      </c>
+      <c r="J14">
+        <v>40</v>
+      </c>
+      <c r="K14">
+        <v>40</v>
+      </c>
+      <c r="L14">
         <v>40</v>
       </c>
     </row>
@@ -1746,7 +1911,7 @@
       </c>
       <c r="C15" s="4">
         <f t="shared" si="3"/>
-        <v>60.634920634920633</v>
+        <v>62.984126984126988</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="4"/>
@@ -1758,13 +1923,25 @@
       </c>
       <c r="F15">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G15">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>188</v>
       </c>
       <c r="H15">
+        <v>40</v>
+      </c>
+      <c r="I15">
+        <v>28</v>
+      </c>
+      <c r="J15">
+        <v>40</v>
+      </c>
+      <c r="K15">
+        <v>40</v>
+      </c>
+      <c r="L15">
         <v>40</v>
       </c>
     </row>
@@ -1777,7 +1954,7 @@
       </c>
       <c r="C16" s="4">
         <f t="shared" si="3"/>
-        <v>60.634920634920633</v>
+        <v>62.682539682539684</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="4"/>
@@ -1789,14 +1966,26 @@
       </c>
       <c r="F16">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="G16">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>169</v>
       </c>
       <c r="H16">
         <v>40</v>
+      </c>
+      <c r="I16">
+        <v>29</v>
+      </c>
+      <c r="J16">
+        <v>40</v>
+      </c>
+      <c r="K16">
+        <v>40</v>
+      </c>
+      <c r="L16">
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:219" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -1808,7 +1997,7 @@
       </c>
       <c r="C17" s="4">
         <f t="shared" si="3"/>
-        <v>60.634920634920633</v>
+        <v>62.222222222222221</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="4"/>
@@ -1820,14 +2009,26 @@
       </c>
       <c r="F17">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="G17">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="H17">
         <v>40</v>
+      </c>
+      <c r="I17">
+        <v>10</v>
+      </c>
+      <c r="J17">
+        <v>40</v>
+      </c>
+      <c r="K17">
+        <v>40</v>
+      </c>
+      <c r="L17">
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:219" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -1839,7 +2040,7 @@
       </c>
       <c r="C18" s="4">
         <f t="shared" si="3"/>
-        <v>60.634920634920633</v>
+        <v>62.698412698412696</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="4"/>
@@ -1851,13 +2052,25 @@
       </c>
       <c r="F18">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G18">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="H18">
+        <v>40</v>
+      </c>
+      <c r="I18">
+        <v>10</v>
+      </c>
+      <c r="J18">
+        <v>40</v>
+      </c>
+      <c r="K18">
+        <v>40</v>
+      </c>
+      <c r="L18">
         <v>40</v>
       </c>
     </row>
@@ -1870,7 +2083,7 @@
       </c>
       <c r="C19" s="4">
         <f t="shared" si="3"/>
-        <v>60.634920634920633</v>
+        <v>62.38095238095238</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="4"/>
@@ -1882,14 +2095,26 @@
       </c>
       <c r="F19">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="G19">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="H19">
         <v>40</v>
+      </c>
+      <c r="I19">
+        <v>10</v>
+      </c>
+      <c r="J19">
+        <v>40</v>
+      </c>
+      <c r="K19">
+        <v>40</v>
+      </c>
+      <c r="L19">
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:219" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -1901,7 +2126,7 @@
       </c>
       <c r="C20" s="4">
         <f t="shared" si="3"/>
-        <v>60.634920634920633</v>
+        <v>63.158730158730158</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="4"/>
@@ -1913,13 +2138,25 @@
       </c>
       <c r="F20">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>199</v>
       </c>
       <c r="H20">
+        <v>40</v>
+      </c>
+      <c r="I20">
+        <v>39</v>
+      </c>
+      <c r="J20">
+        <v>40</v>
+      </c>
+      <c r="K20">
+        <v>40</v>
+      </c>
+      <c r="L20">
         <v>40</v>
       </c>
     </row>
@@ -1932,7 +2169,7 @@
       </c>
       <c r="C21" s="4">
         <f t="shared" si="3"/>
-        <v>60.634920634920633</v>
+        <v>62.063492063492063</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="4"/>
@@ -1944,14 +2181,26 @@
       </c>
       <c r="F21">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="G21">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="H21">
         <v>40</v>
+      </c>
+      <c r="I21">
+        <v>10</v>
+      </c>
+      <c r="J21">
+        <v>40</v>
+      </c>
+      <c r="K21">
+        <v>40</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:219" s="1" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -1963,7 +2212,7 @@
       </c>
       <c r="C22" s="4">
         <f t="shared" si="3"/>
-        <v>60.634920634920633</v>
+        <v>63.031746031746032</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="4"/>
@@ -1975,226 +2224,234 @@
       </c>
       <c r="F22">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G22">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>191</v>
       </c>
       <c r="H22">
         <v>40</v>
       </c>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="6"/>
-      <c r="S22" s="6"/>
-      <c r="T22" s="6"/>
-      <c r="U22" s="6"/>
-      <c r="V22" s="6"/>
-      <c r="W22" s="6"/>
-      <c r="X22" s="6"/>
-      <c r="Y22" s="6"/>
-      <c r="Z22" s="6"/>
-      <c r="AA22" s="6"/>
-      <c r="AB22" s="6"/>
-      <c r="AC22" s="6"/>
-      <c r="AD22" s="6"/>
-      <c r="AE22" s="6"/>
-      <c r="AF22" s="6"/>
-      <c r="AG22" s="6"/>
-      <c r="AH22" s="6"/>
-      <c r="AI22" s="6"/>
-      <c r="AJ22" s="6"/>
-      <c r="AK22" s="6"/>
-      <c r="AL22" s="6"/>
-      <c r="AM22" s="6"/>
-      <c r="AN22" s="6"/>
-      <c r="AO22" s="6"/>
-      <c r="AP22" s="6"/>
-      <c r="AQ22" s="6"/>
-      <c r="AR22" s="6"/>
-      <c r="AS22" s="6"/>
-      <c r="AT22" s="6"/>
-      <c r="AU22" s="6"/>
-      <c r="AV22" s="6"/>
-      <c r="AW22" s="6"/>
-      <c r="AX22" s="6"/>
-      <c r="AY22" s="6"/>
-      <c r="AZ22" s="6"/>
-      <c r="BA22" s="6"/>
-      <c r="BB22" s="6"/>
-      <c r="BC22" s="6"/>
-      <c r="BD22" s="6"/>
-      <c r="BE22" s="6"/>
-      <c r="BF22" s="6"/>
-      <c r="BG22" s="6"/>
-      <c r="BH22" s="6"/>
-      <c r="BI22" s="6"/>
-      <c r="BJ22" s="6"/>
-      <c r="BK22" s="6"/>
-      <c r="BL22" s="6"/>
-      <c r="BM22" s="6"/>
-      <c r="BN22" s="6"/>
-      <c r="BO22" s="6"/>
-      <c r="BP22" s="6"/>
-      <c r="BQ22" s="6"/>
-      <c r="BR22" s="6"/>
-      <c r="BS22" s="6"/>
-      <c r="BT22" s="6"/>
-      <c r="BU22" s="6"/>
-      <c r="BV22" s="6"/>
-      <c r="BW22" s="6"/>
-      <c r="BX22" s="6"/>
-      <c r="BY22" s="6"/>
-      <c r="BZ22" s="6"/>
-      <c r="CA22" s="6"/>
-      <c r="CB22" s="6"/>
-      <c r="CC22" s="6"/>
-      <c r="CD22" s="6"/>
-      <c r="CE22" s="6"/>
-      <c r="CF22" s="6"/>
-      <c r="CG22" s="6"/>
-      <c r="CH22" s="6"/>
-      <c r="CI22" s="6"/>
-      <c r="CJ22" s="6"/>
-      <c r="CK22" s="6"/>
-      <c r="CL22" s="6"/>
-      <c r="CM22" s="6"/>
-      <c r="CN22" s="6"/>
-      <c r="CO22" s="6"/>
-      <c r="CP22" s="6"/>
-      <c r="CQ22" s="6"/>
-      <c r="CR22" s="6"/>
-      <c r="CS22" s="6"/>
-      <c r="CT22" s="6"/>
-      <c r="CU22" s="6"/>
-      <c r="CV22" s="6"/>
-      <c r="CW22" s="6"/>
-      <c r="CX22" s="6"/>
-      <c r="CY22" s="6"/>
-      <c r="CZ22" s="6"/>
-      <c r="DA22" s="6"/>
-      <c r="DB22" s="6"/>
-      <c r="DC22" s="6"/>
-      <c r="DD22" s="6"/>
-      <c r="DE22" s="6"/>
-      <c r="DF22" s="6"/>
-      <c r="DG22" s="6"/>
-      <c r="DH22" s="6"/>
-      <c r="DI22" s="6"/>
-      <c r="DJ22" s="6"/>
-      <c r="DK22" s="6"/>
-      <c r="DL22" s="6"/>
-      <c r="DM22" s="6"/>
-      <c r="DN22" s="6"/>
-      <c r="DO22" s="6"/>
-      <c r="DP22" s="6"/>
-      <c r="DQ22" s="6"/>
-      <c r="DR22" s="6"/>
-      <c r="DS22" s="6"/>
-      <c r="DT22" s="6"/>
-      <c r="DU22" s="6"/>
-      <c r="DV22" s="6"/>
-      <c r="DW22" s="6"/>
-      <c r="DX22" s="6"/>
-      <c r="DY22" s="6"/>
-      <c r="DZ22" s="6"/>
-      <c r="EA22" s="6"/>
-      <c r="EB22" s="6"/>
-      <c r="EC22" s="6"/>
-      <c r="ED22" s="6"/>
-      <c r="EE22" s="6"/>
-      <c r="EF22" s="6"/>
-      <c r="EG22" s="6"/>
-      <c r="EH22" s="6"/>
-      <c r="EI22" s="6"/>
-      <c r="EJ22" s="6"/>
-      <c r="EK22" s="6"/>
-      <c r="EL22" s="6"/>
-      <c r="EM22" s="6"/>
-      <c r="EN22" s="6"/>
-      <c r="EO22" s="6"/>
-      <c r="EP22" s="6"/>
-      <c r="EQ22" s="6"/>
-      <c r="ER22" s="6"/>
-      <c r="ES22" s="6"/>
-      <c r="ET22" s="6"/>
-      <c r="EU22" s="6"/>
-      <c r="EV22" s="6"/>
-      <c r="EW22" s="6"/>
-      <c r="EX22" s="6"/>
-      <c r="EY22" s="6"/>
-      <c r="EZ22" s="6"/>
-      <c r="FA22" s="6"/>
-      <c r="FB22" s="6"/>
-      <c r="FC22" s="6"/>
-      <c r="FD22" s="6"/>
-      <c r="FE22" s="6"/>
-      <c r="FF22" s="6"/>
-      <c r="FG22" s="6"/>
-      <c r="FH22" s="6"/>
-      <c r="FI22" s="6"/>
-      <c r="FJ22" s="6"/>
-      <c r="FK22" s="6"/>
-      <c r="FL22" s="6"/>
-      <c r="FM22" s="6"/>
-      <c r="FN22" s="6"/>
-      <c r="FO22" s="6"/>
-      <c r="FP22" s="6"/>
-      <c r="FQ22" s="6"/>
-      <c r="FR22" s="6"/>
-      <c r="FS22" s="6"/>
-      <c r="FT22" s="6"/>
-      <c r="FU22" s="6"/>
-      <c r="FV22" s="6"/>
-      <c r="FW22" s="6"/>
-      <c r="FX22" s="6"/>
-      <c r="FY22" s="6"/>
-      <c r="FZ22" s="6"/>
-      <c r="GA22" s="6"/>
-      <c r="GB22" s="6"/>
-      <c r="GC22" s="6"/>
-      <c r="GD22" s="6"/>
-      <c r="GE22" s="6"/>
-      <c r="GF22" s="6"/>
-      <c r="GG22" s="6"/>
-      <c r="GH22" s="6"/>
-      <c r="GI22" s="6"/>
-      <c r="GJ22" s="6"/>
-      <c r="GK22" s="6"/>
-      <c r="GL22" s="6"/>
-      <c r="GM22" s="6"/>
-      <c r="GN22" s="6"/>
-      <c r="GO22" s="6"/>
-      <c r="GP22" s="6"/>
-      <c r="GQ22" s="6"/>
-      <c r="GR22" s="6"/>
-      <c r="GS22" s="6"/>
-      <c r="GT22" s="6"/>
-      <c r="GU22" s="6"/>
-      <c r="GV22" s="6"/>
-      <c r="GW22" s="6"/>
-      <c r="GX22" s="6"/>
-      <c r="GY22" s="6"/>
-      <c r="GZ22" s="6"/>
-      <c r="HA22" s="6"/>
-      <c r="HB22" s="6"/>
-      <c r="HC22" s="6"/>
-      <c r="HD22" s="6"/>
-      <c r="HE22" s="6"/>
-      <c r="HF22" s="6"/>
-      <c r="HG22" s="6"/>
-      <c r="HH22" s="6"/>
-      <c r="HI22" s="6"/>
-      <c r="HJ22" s="6"/>
-      <c r="HK22" s="6"/>
+      <c r="I22">
+        <v>31</v>
+      </c>
+      <c r="J22">
+        <v>40</v>
+      </c>
+      <c r="K22">
+        <v>40</v>
+      </c>
+      <c r="L22">
+        <v>40</v>
+      </c>
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22"/>
+      <c r="P22"/>
+      <c r="Q22"/>
+      <c r="R22"/>
+      <c r="S22"/>
+      <c r="T22"/>
+      <c r="U22"/>
+      <c r="V22"/>
+      <c r="W22"/>
+      <c r="X22"/>
+      <c r="Y22"/>
+      <c r="Z22"/>
+      <c r="AA22"/>
+      <c r="AB22"/>
+      <c r="AC22"/>
+      <c r="AD22"/>
+      <c r="AE22"/>
+      <c r="AF22"/>
+      <c r="AG22"/>
+      <c r="AH22"/>
+      <c r="AI22"/>
+      <c r="AJ22"/>
+      <c r="AK22"/>
+      <c r="AL22"/>
+      <c r="AM22"/>
+      <c r="AN22"/>
+      <c r="AO22"/>
+      <c r="AP22"/>
+      <c r="AQ22"/>
+      <c r="AR22"/>
+      <c r="AS22"/>
+      <c r="AT22"/>
+      <c r="AU22"/>
+      <c r="AV22"/>
+      <c r="AW22"/>
+      <c r="AX22"/>
+      <c r="AY22"/>
+      <c r="AZ22"/>
+      <c r="BA22"/>
+      <c r="BB22"/>
+      <c r="BC22"/>
+      <c r="BD22"/>
+      <c r="BE22"/>
+      <c r="BF22"/>
+      <c r="BG22"/>
+      <c r="BH22"/>
+      <c r="BI22"/>
+      <c r="BJ22"/>
+      <c r="BK22"/>
+      <c r="BL22"/>
+      <c r="BM22"/>
+      <c r="BN22"/>
+      <c r="BO22"/>
+      <c r="BP22"/>
+      <c r="BQ22"/>
+      <c r="BR22"/>
+      <c r="BS22"/>
+      <c r="BT22"/>
+      <c r="BU22"/>
+      <c r="BV22"/>
+      <c r="BW22"/>
+      <c r="BX22"/>
+      <c r="BY22"/>
+      <c r="BZ22"/>
+      <c r="CA22"/>
+      <c r="CB22"/>
+      <c r="CC22"/>
+      <c r="CD22"/>
+      <c r="CE22"/>
+      <c r="CF22"/>
+      <c r="CG22"/>
+      <c r="CH22"/>
+      <c r="CI22"/>
+      <c r="CJ22"/>
+      <c r="CK22"/>
+      <c r="CL22"/>
+      <c r="CM22"/>
+      <c r="CN22"/>
+      <c r="CO22"/>
+      <c r="CP22"/>
+      <c r="CQ22"/>
+      <c r="CR22"/>
+      <c r="CS22"/>
+      <c r="CT22"/>
+      <c r="CU22"/>
+      <c r="CV22"/>
+      <c r="CW22"/>
+      <c r="CX22"/>
+      <c r="CY22"/>
+      <c r="CZ22"/>
+      <c r="DA22"/>
+      <c r="DB22"/>
+      <c r="DC22"/>
+      <c r="DD22"/>
+      <c r="DE22"/>
+      <c r="DF22"/>
+      <c r="DG22"/>
+      <c r="DH22"/>
+      <c r="DI22"/>
+      <c r="DJ22"/>
+      <c r="DK22"/>
+      <c r="DL22"/>
+      <c r="DM22"/>
+      <c r="DN22"/>
+      <c r="DO22"/>
+      <c r="DP22"/>
+      <c r="DQ22"/>
+      <c r="DR22"/>
+      <c r="DS22"/>
+      <c r="DT22"/>
+      <c r="DU22"/>
+      <c r="DV22"/>
+      <c r="DW22"/>
+      <c r="DX22"/>
+      <c r="DY22"/>
+      <c r="DZ22"/>
+      <c r="EA22"/>
+      <c r="EB22"/>
+      <c r="EC22"/>
+      <c r="ED22"/>
+      <c r="EE22"/>
+      <c r="EF22"/>
+      <c r="EG22"/>
+      <c r="EH22"/>
+      <c r="EI22"/>
+      <c r="EJ22"/>
+      <c r="EK22"/>
+      <c r="EL22"/>
+      <c r="EM22"/>
+      <c r="EN22"/>
+      <c r="EO22"/>
+      <c r="EP22"/>
+      <c r="EQ22"/>
+      <c r="ER22"/>
+      <c r="ES22"/>
+      <c r="ET22"/>
+      <c r="EU22"/>
+      <c r="EV22"/>
+      <c r="EW22"/>
+      <c r="EX22"/>
+      <c r="EY22"/>
+      <c r="EZ22"/>
+      <c r="FA22"/>
+      <c r="FB22"/>
+      <c r="FC22"/>
+      <c r="FD22"/>
+      <c r="FE22"/>
+      <c r="FF22"/>
+      <c r="FG22"/>
+      <c r="FH22"/>
+      <c r="FI22"/>
+      <c r="FJ22"/>
+      <c r="FK22"/>
+      <c r="FL22"/>
+      <c r="FM22"/>
+      <c r="FN22"/>
+      <c r="FO22"/>
+      <c r="FP22"/>
+      <c r="FQ22"/>
+      <c r="FR22"/>
+      <c r="FS22"/>
+      <c r="FT22"/>
+      <c r="FU22"/>
+      <c r="FV22"/>
+      <c r="FW22"/>
+      <c r="FX22"/>
+      <c r="FY22"/>
+      <c r="FZ22"/>
+      <c r="GA22"/>
+      <c r="GB22"/>
+      <c r="GC22"/>
+      <c r="GD22"/>
+      <c r="GE22"/>
+      <c r="GF22"/>
+      <c r="GG22"/>
+      <c r="GH22"/>
+      <c r="GI22"/>
+      <c r="GJ22"/>
+      <c r="GK22"/>
+      <c r="GL22"/>
+      <c r="GM22"/>
+      <c r="GN22"/>
+      <c r="GO22"/>
+      <c r="GP22"/>
+      <c r="GQ22"/>
+      <c r="GR22"/>
+      <c r="GS22"/>
+      <c r="GT22"/>
+      <c r="GU22"/>
+      <c r="GV22"/>
+      <c r="GW22"/>
+      <c r="GX22"/>
+      <c r="GY22"/>
+      <c r="GZ22"/>
+      <c r="HA22"/>
+      <c r="HB22"/>
+      <c r="HC22"/>
+      <c r="HD22"/>
+      <c r="HE22"/>
+      <c r="HF22"/>
+      <c r="HG22"/>
+      <c r="HH22"/>
+      <c r="HI22"/>
+      <c r="HJ22"/>
+      <c r="HK22"/>
     </row>
     <row r="23" spans="1:219" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23">
@@ -2204,26 +2461,38 @@
         <v>24</v>
       </c>
       <c r="C23" s="4">
-        <f t="shared" ref="C22:C36" si="8">SUM(H23:BR23)/63+60</f>
-        <v>60.634920634920633</v>
+        <f t="shared" ref="C23:C36" si="8">SUM(H23:BR23)/63+60</f>
+        <v>62.873015873015873</v>
       </c>
       <c r="D23" s="4">
-        <f t="shared" ref="D22:D36" si="9">SUM(BS23:EH23)/(131-63)+60</f>
+        <f t="shared" ref="D23:D36" si="9">SUM(BS23:EH23)/(131-63)+60</f>
         <v>60</v>
       </c>
       <c r="E23" s="4">
-        <f t="shared" ref="E22:E36" si="10">SUM(EH23:FV23)/36+60</f>
+        <f t="shared" ref="E23:E36" si="10">SUM(EH23:FV23)/36+60</f>
         <v>60</v>
       </c>
       <c r="F23">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G23">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>181</v>
       </c>
       <c r="H23">
+        <v>40</v>
+      </c>
+      <c r="I23">
+        <v>21</v>
+      </c>
+      <c r="J23">
+        <v>40</v>
+      </c>
+      <c r="K23">
+        <v>40</v>
+      </c>
+      <c r="L23">
         <v>40</v>
       </c>
     </row>
@@ -2236,7 +2505,7 @@
       </c>
       <c r="C24" s="4">
         <f t="shared" si="8"/>
-        <v>60.634920634920633</v>
+        <v>62.698412698412696</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="9"/>
@@ -2248,13 +2517,25 @@
       </c>
       <c r="F24">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G24">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="H24">
+        <v>40</v>
+      </c>
+      <c r="I24">
+        <v>10</v>
+      </c>
+      <c r="J24">
+        <v>40</v>
+      </c>
+      <c r="K24">
+        <v>40</v>
+      </c>
+      <c r="L24">
         <v>40</v>
       </c>
     </row>
@@ -2267,7 +2548,7 @@
       </c>
       <c r="C25" s="4">
         <f t="shared" si="8"/>
-        <v>60.634920634920633</v>
+        <v>62.698412698412696</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="9"/>
@@ -2279,13 +2560,25 @@
       </c>
       <c r="F25">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G25">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="H25">
+        <v>40</v>
+      </c>
+      <c r="I25">
+        <v>10</v>
+      </c>
+      <c r="J25">
+        <v>40</v>
+      </c>
+      <c r="K25">
+        <v>40</v>
+      </c>
+      <c r="L25">
         <v>40</v>
       </c>
     </row>
@@ -2298,7 +2591,7 @@
       </c>
       <c r="C26" s="4">
         <f t="shared" si="8"/>
-        <v>60.634920634920633</v>
+        <v>62.857142857142854</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="9"/>
@@ -2310,13 +2603,25 @@
       </c>
       <c r="F26">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G26">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="H26">
+        <v>40</v>
+      </c>
+      <c r="I26">
+        <v>20</v>
+      </c>
+      <c r="J26">
+        <v>40</v>
+      </c>
+      <c r="K26">
+        <v>40</v>
+      </c>
+      <c r="L26">
         <v>40</v>
       </c>
     </row>
@@ -2329,7 +2634,7 @@
       </c>
       <c r="C27" s="4">
         <f t="shared" si="8"/>
-        <v>60.634920634920633</v>
+        <v>63.174603174603178</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="9"/>
@@ -2345,9 +2650,21 @@
       </c>
       <c r="G27">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="H27">
+        <v>40</v>
+      </c>
+      <c r="I27">
+        <v>40</v>
+      </c>
+      <c r="J27">
+        <v>40</v>
+      </c>
+      <c r="K27">
+        <v>40</v>
+      </c>
+      <c r="L27">
         <v>40</v>
       </c>
     </row>
@@ -2360,7 +2677,7 @@
       </c>
       <c r="C28" s="4">
         <f t="shared" si="8"/>
-        <v>60.634920634920633</v>
+        <v>62.698412698412696</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="9"/>
@@ -2372,13 +2689,25 @@
       </c>
       <c r="F28">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G28">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="H28">
+        <v>40</v>
+      </c>
+      <c r="I28">
+        <v>10</v>
+      </c>
+      <c r="J28">
+        <v>40</v>
+      </c>
+      <c r="K28">
+        <v>40</v>
+      </c>
+      <c r="L28">
         <v>40</v>
       </c>
     </row>
@@ -2391,7 +2720,7 @@
       </c>
       <c r="C29" s="4">
         <f t="shared" si="8"/>
-        <v>60.634920634920633</v>
+        <v>62.936507936507937</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="9"/>
@@ -2403,13 +2732,25 @@
       </c>
       <c r="F29">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G29">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>185</v>
       </c>
       <c r="H29">
+        <v>40</v>
+      </c>
+      <c r="I29">
+        <v>25</v>
+      </c>
+      <c r="J29">
+        <v>40</v>
+      </c>
+      <c r="K29">
+        <v>40</v>
+      </c>
+      <c r="L29">
         <v>40</v>
       </c>
     </row>
@@ -2422,7 +2763,7 @@
       </c>
       <c r="C30" s="4">
         <f t="shared" si="8"/>
-        <v>60.634920634920633</v>
+        <v>62.603174603174601</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="9"/>
@@ -2434,14 +2775,26 @@
       </c>
       <c r="F30">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="G30">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>164</v>
       </c>
       <c r="H30">
         <v>40</v>
+      </c>
+      <c r="I30">
+        <v>24</v>
+      </c>
+      <c r="J30">
+        <v>40</v>
+      </c>
+      <c r="K30">
+        <v>40</v>
+      </c>
+      <c r="L30">
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:219" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -2453,7 +2806,7 @@
       </c>
       <c r="C31" s="4">
         <f t="shared" si="8"/>
-        <v>60.634920634920633</v>
+        <v>62.952380952380949</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="9"/>
@@ -2465,13 +2818,25 @@
       </c>
       <c r="F31">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G31">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>186</v>
       </c>
       <c r="H31">
+        <v>40</v>
+      </c>
+      <c r="I31">
+        <v>26</v>
+      </c>
+      <c r="J31">
+        <v>40</v>
+      </c>
+      <c r="K31">
+        <v>40</v>
+      </c>
+      <c r="L31">
         <v>40</v>
       </c>
     </row>
@@ -2484,7 +2849,7 @@
       </c>
       <c r="C32" s="4">
         <f t="shared" si="8"/>
-        <v>60.634920634920633</v>
+        <v>63.079365079365083</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="9"/>
@@ -2496,13 +2861,25 @@
       </c>
       <c r="F32">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G32">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>194</v>
       </c>
       <c r="H32">
+        <v>40</v>
+      </c>
+      <c r="I32">
+        <v>34</v>
+      </c>
+      <c r="J32">
+        <v>40</v>
+      </c>
+      <c r="K32">
+        <v>40</v>
+      </c>
+      <c r="L32">
         <v>40</v>
       </c>
     </row>
@@ -2515,7 +2892,7 @@
       </c>
       <c r="C33" s="4">
         <f t="shared" si="8"/>
-        <v>60.634920634920633</v>
+        <v>62.968253968253968</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" si="9"/>
@@ -2527,13 +2904,25 @@
       </c>
       <c r="F33">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G33">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>187</v>
       </c>
       <c r="H33">
+        <v>40</v>
+      </c>
+      <c r="I33">
+        <v>27</v>
+      </c>
+      <c r="J33">
+        <v>40</v>
+      </c>
+      <c r="K33">
+        <v>40</v>
+      </c>
+      <c r="L33">
         <v>40</v>
       </c>
     </row>
@@ -2546,7 +2935,7 @@
       </c>
       <c r="C34" s="4">
         <f t="shared" si="8"/>
-        <v>60.634920634920633</v>
+        <v>63.047619047619051</v>
       </c>
       <c r="D34" s="4">
         <f t="shared" si="9"/>
@@ -2558,13 +2947,25 @@
       </c>
       <c r="F34">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G34">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>192</v>
       </c>
       <c r="H34">
+        <v>40</v>
+      </c>
+      <c r="I34">
+        <v>32</v>
+      </c>
+      <c r="J34">
+        <v>40</v>
+      </c>
+      <c r="K34">
+        <v>40</v>
+      </c>
+      <c r="L34">
         <v>40</v>
       </c>
     </row>
@@ -2577,7 +2978,7 @@
       </c>
       <c r="C35" s="4">
         <f t="shared" si="8"/>
-        <v>60.634920634920633</v>
+        <v>63.126984126984127</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="9"/>
@@ -2589,13 +2990,25 @@
       </c>
       <c r="F35">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G35">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>197</v>
       </c>
       <c r="H35">
+        <v>40</v>
+      </c>
+      <c r="I35">
+        <v>37</v>
+      </c>
+      <c r="J35">
+        <v>40</v>
+      </c>
+      <c r="K35">
+        <v>40</v>
+      </c>
+      <c r="L35">
         <v>40</v>
       </c>
     </row>
@@ -2608,7 +3021,7 @@
       </c>
       <c r="C36" s="4">
         <f t="shared" si="8"/>
-        <v>60.634920634920633</v>
+        <v>62.698412698412696</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="9"/>
@@ -2620,13 +3033,25 @@
       </c>
       <c r="F36">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G36">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="H36">
+        <v>40</v>
+      </c>
+      <c r="I36">
+        <v>10</v>
+      </c>
+      <c r="J36">
+        <v>40</v>
+      </c>
+      <c r="K36">
+        <v>40</v>
+      </c>
+      <c r="L36">
         <v>40</v>
       </c>
     </row>
@@ -3234,26 +3659,14 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="G3:G36">
-    <cfRule type="dataBar" priority="4">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{CB878614-6D84-419A-823E-0D450AE98372}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3:QB3 I23 I4:QB21 H4:H36">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="C3:E36">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
-        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
@@ -3270,14 +3683,26 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:E36">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="G3:G36">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{CB878614-6D84-419A-823E-0D450AE98372}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L7:QB21 J7:K36 J3:QB6 H3:I36 L22:L36">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
+        <color rgb="FFFCFCFF"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
@@ -3307,7 +3732,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -3317,7 +3742,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/115 僑生B班.xlsx
+++ b/115 僑生B班.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE362885-9E43-4FBE-B91C-A1C01EE07AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12DB5903-B6F4-46E1-872E-1580E36D94C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>排名</t>
   </si>
@@ -167,6 +167,38 @@
   </si>
   <si>
     <t>中文聽打</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>class0811</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">LED </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>電阻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小型電路試驗板</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GND</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>開始模擬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三顆燈</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -563,7 +595,11 @@
     <col min="4" max="5" width="5.625" style="4" customWidth="1"/>
     <col min="6" max="6" width="4.625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="19" width="5.75" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.5" customWidth="1"/>
+    <col min="15" max="15" width="7.75" customWidth="1"/>
+    <col min="16" max="16" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="5.75" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="6.875" bestFit="1" customWidth="1"/>
     <col min="22" max="29" width="4.875" bestFit="1" customWidth="1"/>
     <col min="30" max="31" width="5.875" bestFit="1" customWidth="1"/>
@@ -623,35 +659,35 @@
       </c>
       <c r="M1" s="2">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>39</v>
       </c>
       <c r="N1" s="2">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>39</v>
       </c>
       <c r="O1" s="2">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>39</v>
       </c>
       <c r="P1" s="2">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>39</v>
       </c>
       <c r="Q1" s="2">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>39</v>
       </c>
       <c r="R1" s="2">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>39</v>
       </c>
       <c r="S1" s="2">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>39</v>
       </c>
       <c r="T1" s="2">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>39</v>
       </c>
       <c r="U1" s="2">
         <f t="shared" si="0"/>
@@ -1385,6 +1421,30 @@
       <c r="L2" s="4" t="s">
         <v>43</v>
       </c>
+      <c r="M2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="3" spans="1:195" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -1395,7 +1455,7 @@
       </c>
       <c r="C3" s="4">
         <f>SUM(H3:BR3)/63+60</f>
-        <v>62.38095238095238</v>
+        <v>67.460317460317455</v>
       </c>
       <c r="D3" s="4">
         <f>SUM(BS3:EH3)/(131-63)+60</f>
@@ -1411,7 +1471,7 @@
       </c>
       <c r="G3">
         <f>SUM(H3:AAB3)</f>
-        <v>150</v>
+        <v>470</v>
       </c>
       <c r="H3">
         <v>40</v>
@@ -1427,6 +1487,30 @@
       </c>
       <c r="L3">
         <v>20</v>
+      </c>
+      <c r="M3">
+        <v>40</v>
+      </c>
+      <c r="N3">
+        <v>40</v>
+      </c>
+      <c r="O3">
+        <v>40</v>
+      </c>
+      <c r="P3">
+        <v>40</v>
+      </c>
+      <c r="Q3">
+        <v>40</v>
+      </c>
+      <c r="R3">
+        <v>40</v>
+      </c>
+      <c r="S3">
+        <v>40</v>
+      </c>
+      <c r="T3">
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:195" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -1438,7 +1522,7 @@
       </c>
       <c r="C4" s="4">
         <f t="shared" ref="C4:C22" si="3">SUM(H4:BR4)/63+60</f>
-        <v>63.142857142857146</v>
+        <v>68.222222222222229</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" ref="D4:D22" si="4">SUM(BS4:EH4)/(131-63)+60</f>
@@ -1454,7 +1538,7 @@
       </c>
       <c r="G4">
         <f t="shared" ref="G4:G36" si="7">SUM(H4:AAB4)</f>
-        <v>198</v>
+        <v>518</v>
       </c>
       <c r="H4">
         <v>40</v>
@@ -1469,6 +1553,30 @@
         <v>40</v>
       </c>
       <c r="L4">
+        <v>40</v>
+      </c>
+      <c r="M4">
+        <v>40</v>
+      </c>
+      <c r="N4">
+        <v>40</v>
+      </c>
+      <c r="O4">
+        <v>40</v>
+      </c>
+      <c r="P4">
+        <v>40</v>
+      </c>
+      <c r="Q4">
+        <v>40</v>
+      </c>
+      <c r="R4">
+        <v>40</v>
+      </c>
+      <c r="S4">
+        <v>40</v>
+      </c>
+      <c r="T4">
         <v>40</v>
       </c>
     </row>
@@ -1481,7 +1589,7 @@
       </c>
       <c r="C5" s="4">
         <f t="shared" si="3"/>
-        <v>62.746031746031747</v>
+        <v>67.825396825396822</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="4"/>
@@ -1497,7 +1605,7 @@
       </c>
       <c r="G5">
         <f t="shared" si="7"/>
-        <v>173</v>
+        <v>493</v>
       </c>
       <c r="H5">
         <v>40</v>
@@ -1513,6 +1621,30 @@
       </c>
       <c r="L5">
         <v>20</v>
+      </c>
+      <c r="M5">
+        <v>40</v>
+      </c>
+      <c r="N5">
+        <v>40</v>
+      </c>
+      <c r="O5">
+        <v>40</v>
+      </c>
+      <c r="P5">
+        <v>40</v>
+      </c>
+      <c r="Q5">
+        <v>40</v>
+      </c>
+      <c r="R5">
+        <v>40</v>
+      </c>
+      <c r="S5">
+        <v>40</v>
+      </c>
+      <c r="T5">
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:195" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -1524,7 +1656,7 @@
       </c>
       <c r="C6" s="4">
         <f t="shared" si="3"/>
-        <v>63.015873015873012</v>
+        <v>68.095238095238102</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="4"/>
@@ -1540,7 +1672,7 @@
       </c>
       <c r="G6">
         <f t="shared" si="7"/>
-        <v>190</v>
+        <v>510</v>
       </c>
       <c r="H6">
         <v>40</v>
@@ -1555,6 +1687,30 @@
         <v>40</v>
       </c>
       <c r="L6">
+        <v>40</v>
+      </c>
+      <c r="M6">
+        <v>40</v>
+      </c>
+      <c r="N6">
+        <v>40</v>
+      </c>
+      <c r="O6">
+        <v>40</v>
+      </c>
+      <c r="P6">
+        <v>40</v>
+      </c>
+      <c r="Q6">
+        <v>40</v>
+      </c>
+      <c r="R6">
+        <v>40</v>
+      </c>
+      <c r="S6">
+        <v>40</v>
+      </c>
+      <c r="T6">
         <v>40</v>
       </c>
     </row>
@@ -1567,7 +1723,7 @@
       </c>
       <c r="C7" s="4">
         <f t="shared" si="3"/>
-        <v>62.698412698412696</v>
+        <v>67.777777777777771</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="4"/>
@@ -1583,7 +1739,7 @@
       </c>
       <c r="G7">
         <f t="shared" si="7"/>
-        <v>170</v>
+        <v>490</v>
       </c>
       <c r="H7">
         <v>40</v>
@@ -1598,6 +1754,30 @@
         <v>40</v>
       </c>
       <c r="L7">
+        <v>40</v>
+      </c>
+      <c r="M7">
+        <v>40</v>
+      </c>
+      <c r="N7">
+        <v>40</v>
+      </c>
+      <c r="O7">
+        <v>40</v>
+      </c>
+      <c r="P7">
+        <v>40</v>
+      </c>
+      <c r="Q7">
+        <v>40</v>
+      </c>
+      <c r="R7">
+        <v>40</v>
+      </c>
+      <c r="S7">
+        <v>40</v>
+      </c>
+      <c r="T7">
         <v>40</v>
       </c>
     </row>
@@ -1610,7 +1790,7 @@
       </c>
       <c r="C8" s="4">
         <f t="shared" si="3"/>
-        <v>62.587301587301589</v>
+        <v>67.666666666666671</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="4"/>
@@ -1626,7 +1806,7 @@
       </c>
       <c r="G8">
         <f t="shared" si="7"/>
-        <v>163</v>
+        <v>483</v>
       </c>
       <c r="H8">
         <v>40</v>
@@ -1642,6 +1822,30 @@
       </c>
       <c r="L8">
         <v>20</v>
+      </c>
+      <c r="M8">
+        <v>40</v>
+      </c>
+      <c r="N8">
+        <v>40</v>
+      </c>
+      <c r="O8">
+        <v>40</v>
+      </c>
+      <c r="P8">
+        <v>40</v>
+      </c>
+      <c r="Q8">
+        <v>40</v>
+      </c>
+      <c r="R8">
+        <v>40</v>
+      </c>
+      <c r="S8">
+        <v>40</v>
+      </c>
+      <c r="T8">
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:195" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -1653,7 +1857,7 @@
       </c>
       <c r="C9" s="4">
         <f t="shared" si="3"/>
-        <v>62.571428571428569</v>
+        <v>67.650793650793645</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="4"/>
@@ -1669,7 +1873,7 @@
       </c>
       <c r="G9">
         <f t="shared" si="7"/>
-        <v>162</v>
+        <v>482</v>
       </c>
       <c r="H9">
         <v>40</v>
@@ -1685,6 +1889,30 @@
       </c>
       <c r="L9">
         <v>20</v>
+      </c>
+      <c r="M9">
+        <v>40</v>
+      </c>
+      <c r="N9">
+        <v>40</v>
+      </c>
+      <c r="O9">
+        <v>40</v>
+      </c>
+      <c r="P9">
+        <v>40</v>
+      </c>
+      <c r="Q9">
+        <v>40</v>
+      </c>
+      <c r="R9">
+        <v>40</v>
+      </c>
+      <c r="S9">
+        <v>40</v>
+      </c>
+      <c r="T9">
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:195" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -1696,7 +1924,7 @@
       </c>
       <c r="C10" s="4">
         <f t="shared" si="3"/>
-        <v>63.111111111111114</v>
+        <v>68.19047619047619</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="4"/>
@@ -1712,7 +1940,7 @@
       </c>
       <c r="G10">
         <f t="shared" si="7"/>
-        <v>196</v>
+        <v>516</v>
       </c>
       <c r="H10">
         <v>40</v>
@@ -1727,6 +1955,30 @@
         <v>40</v>
       </c>
       <c r="L10">
+        <v>40</v>
+      </c>
+      <c r="M10">
+        <v>40</v>
+      </c>
+      <c r="N10">
+        <v>40</v>
+      </c>
+      <c r="O10">
+        <v>40</v>
+      </c>
+      <c r="P10">
+        <v>40</v>
+      </c>
+      <c r="Q10">
+        <v>40</v>
+      </c>
+      <c r="R10">
+        <v>40</v>
+      </c>
+      <c r="S10">
+        <v>40</v>
+      </c>
+      <c r="T10">
         <v>40</v>
       </c>
     </row>
@@ -1739,7 +1991,7 @@
       </c>
       <c r="C11" s="4">
         <f t="shared" si="3"/>
-        <v>62.38095238095238</v>
+        <v>67.460317460317455</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="4"/>
@@ -1755,7 +2007,7 @@
       </c>
       <c r="G11">
         <f t="shared" si="7"/>
-        <v>150</v>
+        <v>470</v>
       </c>
       <c r="H11">
         <v>40</v>
@@ -1771,6 +2023,30 @@
       </c>
       <c r="L11">
         <v>20</v>
+      </c>
+      <c r="M11">
+        <v>40</v>
+      </c>
+      <c r="N11">
+        <v>40</v>
+      </c>
+      <c r="O11">
+        <v>40</v>
+      </c>
+      <c r="P11">
+        <v>40</v>
+      </c>
+      <c r="Q11">
+        <v>40</v>
+      </c>
+      <c r="R11">
+        <v>40</v>
+      </c>
+      <c r="S11">
+        <v>40</v>
+      </c>
+      <c r="T11">
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:195" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -1782,7 +2058,7 @@
       </c>
       <c r="C12" s="4">
         <f t="shared" si="3"/>
-        <v>63.095238095238095</v>
+        <v>68.174603174603178</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="4"/>
@@ -1798,7 +2074,7 @@
       </c>
       <c r="G12">
         <f t="shared" si="7"/>
-        <v>195</v>
+        <v>515</v>
       </c>
       <c r="H12">
         <v>40</v>
@@ -1813,6 +2089,30 @@
         <v>40</v>
       </c>
       <c r="L12">
+        <v>40</v>
+      </c>
+      <c r="M12">
+        <v>40</v>
+      </c>
+      <c r="N12">
+        <v>40</v>
+      </c>
+      <c r="O12">
+        <v>40</v>
+      </c>
+      <c r="P12">
+        <v>40</v>
+      </c>
+      <c r="Q12">
+        <v>40</v>
+      </c>
+      <c r="R12">
+        <v>40</v>
+      </c>
+      <c r="S12">
+        <v>40</v>
+      </c>
+      <c r="T12">
         <v>40</v>
       </c>
     </row>
@@ -1825,7 +2125,7 @@
       </c>
       <c r="C13" s="4">
         <f t="shared" si="3"/>
-        <v>62.38095238095238</v>
+        <v>67.460317460317455</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="4"/>
@@ -1841,7 +2141,7 @@
       </c>
       <c r="G13">
         <f t="shared" si="7"/>
-        <v>150</v>
+        <v>470</v>
       </c>
       <c r="H13">
         <v>40</v>
@@ -1857,6 +2157,30 @@
       </c>
       <c r="L13">
         <v>20</v>
+      </c>
+      <c r="M13">
+        <v>40</v>
+      </c>
+      <c r="N13">
+        <v>40</v>
+      </c>
+      <c r="O13">
+        <v>40</v>
+      </c>
+      <c r="P13">
+        <v>40</v>
+      </c>
+      <c r="Q13">
+        <v>40</v>
+      </c>
+      <c r="R13">
+        <v>40</v>
+      </c>
+      <c r="S13">
+        <v>40</v>
+      </c>
+      <c r="T13">
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:195" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -1868,7 +2192,7 @@
       </c>
       <c r="C14" s="4">
         <f t="shared" si="3"/>
-        <v>62.952380952380949</v>
+        <v>68.031746031746025</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="4"/>
@@ -1884,7 +2208,7 @@
       </c>
       <c r="G14">
         <f t="shared" si="7"/>
-        <v>186</v>
+        <v>506</v>
       </c>
       <c r="H14">
         <v>40</v>
@@ -1899,6 +2223,30 @@
         <v>40</v>
       </c>
       <c r="L14">
+        <v>40</v>
+      </c>
+      <c r="M14">
+        <v>40</v>
+      </c>
+      <c r="N14">
+        <v>40</v>
+      </c>
+      <c r="O14">
+        <v>40</v>
+      </c>
+      <c r="P14">
+        <v>40</v>
+      </c>
+      <c r="Q14">
+        <v>40</v>
+      </c>
+      <c r="R14">
+        <v>40</v>
+      </c>
+      <c r="S14">
+        <v>40</v>
+      </c>
+      <c r="T14">
         <v>40</v>
       </c>
     </row>
@@ -1911,7 +2259,7 @@
       </c>
       <c r="C15" s="4">
         <f t="shared" si="3"/>
-        <v>62.984126984126988</v>
+        <v>68.063492063492063</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="4"/>
@@ -1927,7 +2275,7 @@
       </c>
       <c r="G15">
         <f t="shared" si="7"/>
-        <v>188</v>
+        <v>508</v>
       </c>
       <c r="H15">
         <v>40</v>
@@ -1942,6 +2290,30 @@
         <v>40</v>
       </c>
       <c r="L15">
+        <v>40</v>
+      </c>
+      <c r="M15">
+        <v>40</v>
+      </c>
+      <c r="N15">
+        <v>40</v>
+      </c>
+      <c r="O15">
+        <v>40</v>
+      </c>
+      <c r="P15">
+        <v>40</v>
+      </c>
+      <c r="Q15">
+        <v>40</v>
+      </c>
+      <c r="R15">
+        <v>40</v>
+      </c>
+      <c r="S15">
+        <v>40</v>
+      </c>
+      <c r="T15">
         <v>40</v>
       </c>
     </row>
@@ -1954,7 +2326,7 @@
       </c>
       <c r="C16" s="4">
         <f t="shared" si="3"/>
-        <v>62.682539682539684</v>
+        <v>67.761904761904759</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="4"/>
@@ -1970,7 +2342,7 @@
       </c>
       <c r="G16">
         <f t="shared" si="7"/>
-        <v>169</v>
+        <v>489</v>
       </c>
       <c r="H16">
         <v>40</v>
@@ -1986,6 +2358,30 @@
       </c>
       <c r="L16">
         <v>20</v>
+      </c>
+      <c r="M16">
+        <v>40</v>
+      </c>
+      <c r="N16">
+        <v>40</v>
+      </c>
+      <c r="O16">
+        <v>40</v>
+      </c>
+      <c r="P16">
+        <v>40</v>
+      </c>
+      <c r="Q16">
+        <v>40</v>
+      </c>
+      <c r="R16">
+        <v>40</v>
+      </c>
+      <c r="S16">
+        <v>40</v>
+      </c>
+      <c r="T16">
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:219" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -1997,7 +2393,7 @@
       </c>
       <c r="C17" s="4">
         <f t="shared" si="3"/>
-        <v>62.222222222222221</v>
+        <v>67.301587301587304</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="4"/>
@@ -2013,7 +2409,7 @@
       </c>
       <c r="G17">
         <f t="shared" si="7"/>
-        <v>140</v>
+        <v>460</v>
       </c>
       <c r="H17">
         <v>40</v>
@@ -2029,6 +2425,30 @@
       </c>
       <c r="L17">
         <v>10</v>
+      </c>
+      <c r="M17">
+        <v>40</v>
+      </c>
+      <c r="N17">
+        <v>40</v>
+      </c>
+      <c r="O17">
+        <v>40</v>
+      </c>
+      <c r="P17">
+        <v>40</v>
+      </c>
+      <c r="Q17">
+        <v>40</v>
+      </c>
+      <c r="R17">
+        <v>40</v>
+      </c>
+      <c r="S17">
+        <v>40</v>
+      </c>
+      <c r="T17">
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:219" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -2040,7 +2460,7 @@
       </c>
       <c r="C18" s="4">
         <f t="shared" si="3"/>
-        <v>62.698412698412696</v>
+        <v>67.777777777777771</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="4"/>
@@ -2056,7 +2476,7 @@
       </c>
       <c r="G18">
         <f t="shared" si="7"/>
-        <v>170</v>
+        <v>490</v>
       </c>
       <c r="H18">
         <v>40</v>
@@ -2071,6 +2491,30 @@
         <v>40</v>
       </c>
       <c r="L18">
+        <v>40</v>
+      </c>
+      <c r="M18">
+        <v>40</v>
+      </c>
+      <c r="N18">
+        <v>40</v>
+      </c>
+      <c r="O18">
+        <v>40</v>
+      </c>
+      <c r="P18">
+        <v>40</v>
+      </c>
+      <c r="Q18">
+        <v>40</v>
+      </c>
+      <c r="R18">
+        <v>40</v>
+      </c>
+      <c r="S18">
+        <v>40</v>
+      </c>
+      <c r="T18">
         <v>40</v>
       </c>
     </row>
@@ -2083,7 +2527,7 @@
       </c>
       <c r="C19" s="4">
         <f t="shared" si="3"/>
-        <v>62.38095238095238</v>
+        <v>67.460317460317455</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="4"/>
@@ -2099,7 +2543,7 @@
       </c>
       <c r="G19">
         <f t="shared" si="7"/>
-        <v>150</v>
+        <v>470</v>
       </c>
       <c r="H19">
         <v>40</v>
@@ -2115,6 +2559,30 @@
       </c>
       <c r="L19">
         <v>20</v>
+      </c>
+      <c r="M19">
+        <v>40</v>
+      </c>
+      <c r="N19">
+        <v>40</v>
+      </c>
+      <c r="O19">
+        <v>40</v>
+      </c>
+      <c r="P19">
+        <v>40</v>
+      </c>
+      <c r="Q19">
+        <v>40</v>
+      </c>
+      <c r="R19">
+        <v>40</v>
+      </c>
+      <c r="S19">
+        <v>40</v>
+      </c>
+      <c r="T19">
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:219" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -2126,7 +2594,7 @@
       </c>
       <c r="C20" s="4">
         <f t="shared" si="3"/>
-        <v>63.158730158730158</v>
+        <v>68.238095238095241</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="4"/>
@@ -2142,7 +2610,7 @@
       </c>
       <c r="G20">
         <f t="shared" si="7"/>
-        <v>199</v>
+        <v>519</v>
       </c>
       <c r="H20">
         <v>40</v>
@@ -2157,6 +2625,30 @@
         <v>40</v>
       </c>
       <c r="L20">
+        <v>40</v>
+      </c>
+      <c r="M20">
+        <v>40</v>
+      </c>
+      <c r="N20">
+        <v>40</v>
+      </c>
+      <c r="O20">
+        <v>40</v>
+      </c>
+      <c r="P20">
+        <v>40</v>
+      </c>
+      <c r="Q20">
+        <v>40</v>
+      </c>
+      <c r="R20">
+        <v>40</v>
+      </c>
+      <c r="S20">
+        <v>40</v>
+      </c>
+      <c r="T20">
         <v>40</v>
       </c>
     </row>
@@ -2169,7 +2661,7 @@
       </c>
       <c r="C21" s="4">
         <f t="shared" si="3"/>
-        <v>62.063492063492063</v>
+        <v>67.142857142857139</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="4"/>
@@ -2185,7 +2677,7 @@
       </c>
       <c r="G21">
         <f t="shared" si="7"/>
-        <v>130</v>
+        <v>450</v>
       </c>
       <c r="H21">
         <v>40</v>
@@ -2201,6 +2693,30 @@
       </c>
       <c r="L21">
         <v>0</v>
+      </c>
+      <c r="M21">
+        <v>40</v>
+      </c>
+      <c r="N21">
+        <v>40</v>
+      </c>
+      <c r="O21">
+        <v>40</v>
+      </c>
+      <c r="P21">
+        <v>40</v>
+      </c>
+      <c r="Q21">
+        <v>40</v>
+      </c>
+      <c r="R21">
+        <v>40</v>
+      </c>
+      <c r="S21">
+        <v>40</v>
+      </c>
+      <c r="T21">
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:219" s="1" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -2212,7 +2728,7 @@
       </c>
       <c r="C22" s="4">
         <f t="shared" si="3"/>
-        <v>63.031746031746032</v>
+        <v>68.111111111111114</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="4"/>
@@ -2228,7 +2744,7 @@
       </c>
       <c r="G22">
         <f t="shared" si="7"/>
-        <v>191</v>
+        <v>511</v>
       </c>
       <c r="H22">
         <v>40</v>
@@ -2245,14 +2761,30 @@
       <c r="L22">
         <v>40</v>
       </c>
-      <c r="M22"/>
-      <c r="N22"/>
-      <c r="O22"/>
-      <c r="P22"/>
-      <c r="Q22"/>
-      <c r="R22"/>
-      <c r="S22"/>
-      <c r="T22"/>
+      <c r="M22">
+        <v>40</v>
+      </c>
+      <c r="N22">
+        <v>40</v>
+      </c>
+      <c r="O22">
+        <v>40</v>
+      </c>
+      <c r="P22">
+        <v>40</v>
+      </c>
+      <c r="Q22">
+        <v>40</v>
+      </c>
+      <c r="R22">
+        <v>40</v>
+      </c>
+      <c r="S22">
+        <v>40</v>
+      </c>
+      <c r="T22">
+        <v>40</v>
+      </c>
       <c r="U22"/>
       <c r="V22"/>
       <c r="W22"/>
@@ -2462,7 +2994,7 @@
       </c>
       <c r="C23" s="4">
         <f t="shared" ref="C23:C36" si="8">SUM(H23:BR23)/63+60</f>
-        <v>62.873015873015873</v>
+        <v>67.952380952380949</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" ref="D23:D36" si="9">SUM(BS23:EH23)/(131-63)+60</f>
@@ -2478,7 +3010,7 @@
       </c>
       <c r="G23">
         <f t="shared" si="7"/>
-        <v>181</v>
+        <v>501</v>
       </c>
       <c r="H23">
         <v>40</v>
@@ -2493,6 +3025,30 @@
         <v>40</v>
       </c>
       <c r="L23">
+        <v>40</v>
+      </c>
+      <c r="M23">
+        <v>40</v>
+      </c>
+      <c r="N23">
+        <v>40</v>
+      </c>
+      <c r="O23">
+        <v>40</v>
+      </c>
+      <c r="P23">
+        <v>40</v>
+      </c>
+      <c r="Q23">
+        <v>40</v>
+      </c>
+      <c r="R23">
+        <v>40</v>
+      </c>
+      <c r="S23">
+        <v>40</v>
+      </c>
+      <c r="T23">
         <v>40</v>
       </c>
     </row>
@@ -2505,7 +3061,7 @@
       </c>
       <c r="C24" s="4">
         <f t="shared" si="8"/>
-        <v>62.698412698412696</v>
+        <v>67.777777777777771</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="9"/>
@@ -2521,7 +3077,7 @@
       </c>
       <c r="G24">
         <f t="shared" si="7"/>
-        <v>170</v>
+        <v>490</v>
       </c>
       <c r="H24">
         <v>40</v>
@@ -2536,6 +3092,30 @@
         <v>40</v>
       </c>
       <c r="L24">
+        <v>40</v>
+      </c>
+      <c r="M24">
+        <v>40</v>
+      </c>
+      <c r="N24">
+        <v>40</v>
+      </c>
+      <c r="O24">
+        <v>40</v>
+      </c>
+      <c r="P24">
+        <v>40</v>
+      </c>
+      <c r="Q24">
+        <v>40</v>
+      </c>
+      <c r="R24">
+        <v>40</v>
+      </c>
+      <c r="S24">
+        <v>40</v>
+      </c>
+      <c r="T24">
         <v>40</v>
       </c>
     </row>
@@ -2548,7 +3128,7 @@
       </c>
       <c r="C25" s="4">
         <f t="shared" si="8"/>
-        <v>62.698412698412696</v>
+        <v>67.777777777777771</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="9"/>
@@ -2564,7 +3144,7 @@
       </c>
       <c r="G25">
         <f t="shared" si="7"/>
-        <v>170</v>
+        <v>490</v>
       </c>
       <c r="H25">
         <v>40</v>
@@ -2579,6 +3159,30 @@
         <v>40</v>
       </c>
       <c r="L25">
+        <v>40</v>
+      </c>
+      <c r="M25">
+        <v>40</v>
+      </c>
+      <c r="N25">
+        <v>40</v>
+      </c>
+      <c r="O25">
+        <v>40</v>
+      </c>
+      <c r="P25">
+        <v>40</v>
+      </c>
+      <c r="Q25">
+        <v>40</v>
+      </c>
+      <c r="R25">
+        <v>40</v>
+      </c>
+      <c r="S25">
+        <v>40</v>
+      </c>
+      <c r="T25">
         <v>40</v>
       </c>
     </row>
@@ -2591,7 +3195,7 @@
       </c>
       <c r="C26" s="4">
         <f t="shared" si="8"/>
-        <v>62.857142857142854</v>
+        <v>67.936507936507937</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="9"/>
@@ -2607,7 +3211,7 @@
       </c>
       <c r="G26">
         <f t="shared" si="7"/>
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="H26">
         <v>40</v>
@@ -2622,6 +3226,30 @@
         <v>40</v>
       </c>
       <c r="L26">
+        <v>40</v>
+      </c>
+      <c r="M26">
+        <v>40</v>
+      </c>
+      <c r="N26">
+        <v>40</v>
+      </c>
+      <c r="O26">
+        <v>40</v>
+      </c>
+      <c r="P26">
+        <v>40</v>
+      </c>
+      <c r="Q26">
+        <v>40</v>
+      </c>
+      <c r="R26">
+        <v>40</v>
+      </c>
+      <c r="S26">
+        <v>40</v>
+      </c>
+      <c r="T26">
         <v>40</v>
       </c>
     </row>
@@ -2634,7 +3262,7 @@
       </c>
       <c r="C27" s="4">
         <f t="shared" si="8"/>
-        <v>63.174603174603178</v>
+        <v>68.253968253968253</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="9"/>
@@ -2650,7 +3278,7 @@
       </c>
       <c r="G27">
         <f t="shared" si="7"/>
-        <v>200</v>
+        <v>520</v>
       </c>
       <c r="H27">
         <v>40</v>
@@ -2665,6 +3293,30 @@
         <v>40</v>
       </c>
       <c r="L27">
+        <v>40</v>
+      </c>
+      <c r="M27">
+        <v>40</v>
+      </c>
+      <c r="N27">
+        <v>40</v>
+      </c>
+      <c r="O27">
+        <v>40</v>
+      </c>
+      <c r="P27">
+        <v>40</v>
+      </c>
+      <c r="Q27">
+        <v>40</v>
+      </c>
+      <c r="R27">
+        <v>40</v>
+      </c>
+      <c r="S27">
+        <v>40</v>
+      </c>
+      <c r="T27">
         <v>40</v>
       </c>
     </row>
@@ -2677,7 +3329,7 @@
       </c>
       <c r="C28" s="4">
         <f t="shared" si="8"/>
-        <v>62.698412698412696</v>
+        <v>67.777777777777771</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="9"/>
@@ -2693,7 +3345,7 @@
       </c>
       <c r="G28">
         <f t="shared" si="7"/>
-        <v>170</v>
+        <v>490</v>
       </c>
       <c r="H28">
         <v>40</v>
@@ -2708,6 +3360,30 @@
         <v>40</v>
       </c>
       <c r="L28">
+        <v>40</v>
+      </c>
+      <c r="M28">
+        <v>40</v>
+      </c>
+      <c r="N28">
+        <v>40</v>
+      </c>
+      <c r="O28">
+        <v>40</v>
+      </c>
+      <c r="P28">
+        <v>40</v>
+      </c>
+      <c r="Q28">
+        <v>40</v>
+      </c>
+      <c r="R28">
+        <v>40</v>
+      </c>
+      <c r="S28">
+        <v>40</v>
+      </c>
+      <c r="T28">
         <v>40</v>
       </c>
     </row>
@@ -2720,7 +3396,7 @@
       </c>
       <c r="C29" s="4">
         <f t="shared" si="8"/>
-        <v>62.936507936507937</v>
+        <v>68.015873015873012</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="9"/>
@@ -2736,7 +3412,7 @@
       </c>
       <c r="G29">
         <f t="shared" si="7"/>
-        <v>185</v>
+        <v>505</v>
       </c>
       <c r="H29">
         <v>40</v>
@@ -2751,6 +3427,30 @@
         <v>40</v>
       </c>
       <c r="L29">
+        <v>40</v>
+      </c>
+      <c r="M29">
+        <v>40</v>
+      </c>
+      <c r="N29">
+        <v>40</v>
+      </c>
+      <c r="O29">
+        <v>40</v>
+      </c>
+      <c r="P29">
+        <v>40</v>
+      </c>
+      <c r="Q29">
+        <v>40</v>
+      </c>
+      <c r="R29">
+        <v>40</v>
+      </c>
+      <c r="S29">
+        <v>40</v>
+      </c>
+      <c r="T29">
         <v>40</v>
       </c>
     </row>
@@ -2763,7 +3463,7 @@
       </c>
       <c r="C30" s="4">
         <f t="shared" si="8"/>
-        <v>62.603174603174601</v>
+        <v>67.682539682539684</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="9"/>
@@ -2779,7 +3479,7 @@
       </c>
       <c r="G30">
         <f t="shared" si="7"/>
-        <v>164</v>
+        <v>484</v>
       </c>
       <c r="H30">
         <v>40</v>
@@ -2795,6 +3495,30 @@
       </c>
       <c r="L30">
         <v>20</v>
+      </c>
+      <c r="M30">
+        <v>40</v>
+      </c>
+      <c r="N30">
+        <v>40</v>
+      </c>
+      <c r="O30">
+        <v>40</v>
+      </c>
+      <c r="P30">
+        <v>40</v>
+      </c>
+      <c r="Q30">
+        <v>40</v>
+      </c>
+      <c r="R30">
+        <v>40</v>
+      </c>
+      <c r="S30">
+        <v>40</v>
+      </c>
+      <c r="T30">
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:219" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -2806,7 +3530,7 @@
       </c>
       <c r="C31" s="4">
         <f t="shared" si="8"/>
-        <v>62.952380952380949</v>
+        <v>68.031746031746025</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="9"/>
@@ -2822,7 +3546,7 @@
       </c>
       <c r="G31">
         <f t="shared" si="7"/>
-        <v>186</v>
+        <v>506</v>
       </c>
       <c r="H31">
         <v>40</v>
@@ -2837,6 +3561,30 @@
         <v>40</v>
       </c>
       <c r="L31">
+        <v>40</v>
+      </c>
+      <c r="M31">
+        <v>40</v>
+      </c>
+      <c r="N31">
+        <v>40</v>
+      </c>
+      <c r="O31">
+        <v>40</v>
+      </c>
+      <c r="P31">
+        <v>40</v>
+      </c>
+      <c r="Q31">
+        <v>40</v>
+      </c>
+      <c r="R31">
+        <v>40</v>
+      </c>
+      <c r="S31">
+        <v>40</v>
+      </c>
+      <c r="T31">
         <v>40</v>
       </c>
     </row>
@@ -2849,7 +3597,7 @@
       </c>
       <c r="C32" s="4">
         <f t="shared" si="8"/>
-        <v>63.079365079365083</v>
+        <v>68.158730158730151</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="9"/>
@@ -2865,7 +3613,7 @@
       </c>
       <c r="G32">
         <f t="shared" si="7"/>
-        <v>194</v>
+        <v>514</v>
       </c>
       <c r="H32">
         <v>40</v>
@@ -2880,6 +3628,30 @@
         <v>40</v>
       </c>
       <c r="L32">
+        <v>40</v>
+      </c>
+      <c r="M32">
+        <v>40</v>
+      </c>
+      <c r="N32">
+        <v>40</v>
+      </c>
+      <c r="O32">
+        <v>40</v>
+      </c>
+      <c r="P32">
+        <v>40</v>
+      </c>
+      <c r="Q32">
+        <v>40</v>
+      </c>
+      <c r="R32">
+        <v>40</v>
+      </c>
+      <c r="S32">
+        <v>40</v>
+      </c>
+      <c r="T32">
         <v>40</v>
       </c>
     </row>
@@ -2892,7 +3664,7 @@
       </c>
       <c r="C33" s="4">
         <f t="shared" si="8"/>
-        <v>62.968253968253968</v>
+        <v>68.047619047619051</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" si="9"/>
@@ -2908,7 +3680,7 @@
       </c>
       <c r="G33">
         <f t="shared" si="7"/>
-        <v>187</v>
+        <v>507</v>
       </c>
       <c r="H33">
         <v>40</v>
@@ -2923,6 +3695,30 @@
         <v>40</v>
       </c>
       <c r="L33">
+        <v>40</v>
+      </c>
+      <c r="M33">
+        <v>40</v>
+      </c>
+      <c r="N33">
+        <v>40</v>
+      </c>
+      <c r="O33">
+        <v>40</v>
+      </c>
+      <c r="P33">
+        <v>40</v>
+      </c>
+      <c r="Q33">
+        <v>40</v>
+      </c>
+      <c r="R33">
+        <v>40</v>
+      </c>
+      <c r="S33">
+        <v>40</v>
+      </c>
+      <c r="T33">
         <v>40</v>
       </c>
     </row>
@@ -2935,7 +3731,7 @@
       </c>
       <c r="C34" s="4">
         <f t="shared" si="8"/>
-        <v>63.047619047619051</v>
+        <v>68.126984126984127</v>
       </c>
       <c r="D34" s="4">
         <f t="shared" si="9"/>
@@ -2951,7 +3747,7 @@
       </c>
       <c r="G34">
         <f t="shared" si="7"/>
-        <v>192</v>
+        <v>512</v>
       </c>
       <c r="H34">
         <v>40</v>
@@ -2966,6 +3762,30 @@
         <v>40</v>
       </c>
       <c r="L34">
+        <v>40</v>
+      </c>
+      <c r="M34">
+        <v>40</v>
+      </c>
+      <c r="N34">
+        <v>40</v>
+      </c>
+      <c r="O34">
+        <v>40</v>
+      </c>
+      <c r="P34">
+        <v>40</v>
+      </c>
+      <c r="Q34">
+        <v>40</v>
+      </c>
+      <c r="R34">
+        <v>40</v>
+      </c>
+      <c r="S34">
+        <v>40</v>
+      </c>
+      <c r="T34">
         <v>40</v>
       </c>
     </row>
@@ -2978,7 +3798,7 @@
       </c>
       <c r="C35" s="4">
         <f t="shared" si="8"/>
-        <v>63.126984126984127</v>
+        <v>68.206349206349202</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="9"/>
@@ -2994,7 +3814,7 @@
       </c>
       <c r="G35">
         <f t="shared" si="7"/>
-        <v>197</v>
+        <v>517</v>
       </c>
       <c r="H35">
         <v>40</v>
@@ -3009,6 +3829,30 @@
         <v>40</v>
       </c>
       <c r="L35">
+        <v>40</v>
+      </c>
+      <c r="M35">
+        <v>40</v>
+      </c>
+      <c r="N35">
+        <v>40</v>
+      </c>
+      <c r="O35">
+        <v>40</v>
+      </c>
+      <c r="P35">
+        <v>40</v>
+      </c>
+      <c r="Q35">
+        <v>40</v>
+      </c>
+      <c r="R35">
+        <v>40</v>
+      </c>
+      <c r="S35">
+        <v>40</v>
+      </c>
+      <c r="T35">
         <v>40</v>
       </c>
     </row>
@@ -3021,7 +3865,7 @@
       </c>
       <c r="C36" s="4">
         <f t="shared" si="8"/>
-        <v>62.698412698412696</v>
+        <v>67.777777777777771</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="9"/>
@@ -3037,7 +3881,7 @@
       </c>
       <c r="G36">
         <f t="shared" si="7"/>
-        <v>170</v>
+        <v>490</v>
       </c>
       <c r="H36">
         <v>40</v>
@@ -3052,6 +3896,30 @@
         <v>40</v>
       </c>
       <c r="L36">
+        <v>40</v>
+      </c>
+      <c r="M36">
+        <v>40</v>
+      </c>
+      <c r="N36">
+        <v>40</v>
+      </c>
+      <c r="O36">
+        <v>40</v>
+      </c>
+      <c r="P36">
+        <v>40</v>
+      </c>
+      <c r="Q36">
+        <v>40</v>
+      </c>
+      <c r="R36">
+        <v>40</v>
+      </c>
+      <c r="S36">
+        <v>40</v>
+      </c>
+      <c r="T36">
         <v>40</v>
       </c>
     </row>
@@ -3697,7 +4565,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L7:QB21 J7:K36 J3:QB6 H3:I36 L22:L36">
+  <conditionalFormatting sqref="H3:I36 J3:QB3 U4:QB21 J4:T36">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>

--- a/115 僑生B班.xlsx
+++ b/115 僑生B班.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12DB5903-B6F4-46E1-872E-1580E36D94C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9972A060-0FEF-4AE8-A269-D769A782C4E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>排名</t>
   </si>
@@ -81,9 +81,6 @@
   </si>
   <si>
     <t>徐德勝</t>
-  </si>
-  <si>
-    <t>陳泰寶</t>
   </si>
   <si>
     <t>陳雄</t>
@@ -199,6 +196,22 @@
   </si>
   <si>
     <t>三顆燈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>class0812</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>class0813</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>class0814</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>class0817</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -600,8 +613,8 @@
     <col min="16" max="16" width="16.125" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="5.75" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.875" bestFit="1" customWidth="1"/>
-    <col min="22" max="29" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="24" max="29" width="4.875" bestFit="1" customWidth="1"/>
     <col min="30" max="31" width="5.875" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="13.875" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="23.5" bestFit="1" customWidth="1"/>
@@ -691,19 +704,19 @@
       </c>
       <c r="U1" s="2">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>39</v>
       </c>
       <c r="V1" s="2">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>39</v>
       </c>
       <c r="W1" s="2">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>39</v>
       </c>
       <c r="X1" s="2">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>39</v>
       </c>
       <c r="Y1" s="2">
         <f t="shared" si="0"/>
@@ -1392,7 +1405,7 @@
     </row>
     <row r="2" spans="1:195" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>1</v>
@@ -1407,43 +1420,55 @@
         <v>0</v>
       </c>
       <c r="H2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="J2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="R2" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="S2" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="T2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>51</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:195" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -1455,7 +1480,7 @@
       </c>
       <c r="C3" s="4">
         <f>SUM(H3:BR3)/63+60</f>
-        <v>67.460317460317455</v>
+        <v>70</v>
       </c>
       <c r="D3" s="4">
         <f>SUM(BS3:EH3)/(131-63)+60</f>
@@ -1467,11 +1492,11 @@
       </c>
       <c r="F3">
         <f>RANK(G3,$G$3:$G$36)</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G3">
         <f>SUM(H3:AAB3)</f>
-        <v>470</v>
+        <v>630</v>
       </c>
       <c r="H3">
         <v>40</v>
@@ -1510,6 +1535,18 @@
         <v>40</v>
       </c>
       <c r="T3">
+        <v>40</v>
+      </c>
+      <c r="U3">
+        <v>40</v>
+      </c>
+      <c r="V3">
+        <v>40</v>
+      </c>
+      <c r="W3">
+        <v>40</v>
+      </c>
+      <c r="X3">
         <v>40</v>
       </c>
     </row>
@@ -1522,7 +1559,7 @@
       </c>
       <c r="C4" s="4">
         <f t="shared" ref="C4:C22" si="3">SUM(H4:BR4)/63+60</f>
-        <v>68.222222222222229</v>
+        <v>70.761904761904759</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" ref="D4:D22" si="4">SUM(BS4:EH4)/(131-63)+60</f>
@@ -1538,7 +1575,7 @@
       </c>
       <c r="G4">
         <f t="shared" ref="G4:G36" si="7">SUM(H4:AAB4)</f>
-        <v>518</v>
+        <v>678</v>
       </c>
       <c r="H4">
         <v>40</v>
@@ -1577,6 +1614,18 @@
         <v>40</v>
       </c>
       <c r="T4">
+        <v>40</v>
+      </c>
+      <c r="U4">
+        <v>40</v>
+      </c>
+      <c r="V4">
+        <v>40</v>
+      </c>
+      <c r="W4">
+        <v>40</v>
+      </c>
+      <c r="X4">
         <v>40</v>
       </c>
     </row>
@@ -1589,7 +1638,7 @@
       </c>
       <c r="C5" s="4">
         <f t="shared" si="3"/>
-        <v>67.825396825396822</v>
+        <v>70.365079365079367</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="4"/>
@@ -1605,7 +1654,7 @@
       </c>
       <c r="G5">
         <f t="shared" si="7"/>
-        <v>493</v>
+        <v>653</v>
       </c>
       <c r="H5">
         <v>40</v>
@@ -1644,6 +1693,18 @@
         <v>40</v>
       </c>
       <c r="T5">
+        <v>40</v>
+      </c>
+      <c r="U5">
+        <v>40</v>
+      </c>
+      <c r="V5">
+        <v>40</v>
+      </c>
+      <c r="W5">
+        <v>40</v>
+      </c>
+      <c r="X5">
         <v>40</v>
       </c>
     </row>
@@ -1656,7 +1717,7 @@
       </c>
       <c r="C6" s="4">
         <f t="shared" si="3"/>
-        <v>68.095238095238102</v>
+        <v>70.634920634920633</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="4"/>
@@ -1672,7 +1733,7 @@
       </c>
       <c r="G6">
         <f t="shared" si="7"/>
-        <v>510</v>
+        <v>670</v>
       </c>
       <c r="H6">
         <v>40</v>
@@ -1711,6 +1772,18 @@
         <v>40</v>
       </c>
       <c r="T6">
+        <v>40</v>
+      </c>
+      <c r="U6">
+        <v>40</v>
+      </c>
+      <c r="V6">
+        <v>40</v>
+      </c>
+      <c r="W6">
+        <v>40</v>
+      </c>
+      <c r="X6">
         <v>40</v>
       </c>
     </row>
@@ -1723,7 +1796,7 @@
       </c>
       <c r="C7" s="4">
         <f t="shared" si="3"/>
-        <v>67.777777777777771</v>
+        <v>70.317460317460316</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="4"/>
@@ -1739,7 +1812,7 @@
       </c>
       <c r="G7">
         <f t="shared" si="7"/>
-        <v>490</v>
+        <v>650</v>
       </c>
       <c r="H7">
         <v>40</v>
@@ -1778,6 +1851,18 @@
         <v>40</v>
       </c>
       <c r="T7">
+        <v>40</v>
+      </c>
+      <c r="U7">
+        <v>40</v>
+      </c>
+      <c r="V7">
+        <v>40</v>
+      </c>
+      <c r="W7">
+        <v>40</v>
+      </c>
+      <c r="X7">
         <v>40</v>
       </c>
     </row>
@@ -1790,7 +1875,7 @@
       </c>
       <c r="C8" s="4">
         <f t="shared" si="3"/>
-        <v>67.666666666666671</v>
+        <v>70.206349206349202</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="4"/>
@@ -1802,11 +1887,11 @@
       </c>
       <c r="F8">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G8">
         <f t="shared" si="7"/>
-        <v>483</v>
+        <v>643</v>
       </c>
       <c r="H8">
         <v>40</v>
@@ -1845,6 +1930,18 @@
         <v>40</v>
       </c>
       <c r="T8">
+        <v>40</v>
+      </c>
+      <c r="U8">
+        <v>40</v>
+      </c>
+      <c r="V8">
+        <v>40</v>
+      </c>
+      <c r="W8">
+        <v>40</v>
+      </c>
+      <c r="X8">
         <v>40</v>
       </c>
     </row>
@@ -1857,7 +1954,7 @@
       </c>
       <c r="C9" s="4">
         <f t="shared" si="3"/>
-        <v>67.650793650793645</v>
+        <v>70.19047619047619</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="4"/>
@@ -1869,11 +1966,11 @@
       </c>
       <c r="F9">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G9">
         <f t="shared" si="7"/>
-        <v>482</v>
+        <v>642</v>
       </c>
       <c r="H9">
         <v>40</v>
@@ -1912,6 +2009,18 @@
         <v>40</v>
       </c>
       <c r="T9">
+        <v>40</v>
+      </c>
+      <c r="U9">
+        <v>40</v>
+      </c>
+      <c r="V9">
+        <v>40</v>
+      </c>
+      <c r="W9">
+        <v>40</v>
+      </c>
+      <c r="X9">
         <v>40</v>
       </c>
     </row>
@@ -1924,7 +2033,7 @@
       </c>
       <c r="C10" s="4">
         <f t="shared" si="3"/>
-        <v>68.19047619047619</v>
+        <v>70.730158730158735</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="4"/>
@@ -1940,7 +2049,7 @@
       </c>
       <c r="G10">
         <f t="shared" si="7"/>
-        <v>516</v>
+        <v>676</v>
       </c>
       <c r="H10">
         <v>40</v>
@@ -1979,6 +2088,18 @@
         <v>40</v>
       </c>
       <c r="T10">
+        <v>40</v>
+      </c>
+      <c r="U10">
+        <v>40</v>
+      </c>
+      <c r="V10">
+        <v>40</v>
+      </c>
+      <c r="W10">
+        <v>40</v>
+      </c>
+      <c r="X10">
         <v>40</v>
       </c>
     </row>
@@ -1991,7 +2112,7 @@
       </c>
       <c r="C11" s="4">
         <f t="shared" si="3"/>
-        <v>67.460317460317455</v>
+        <v>70</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="4"/>
@@ -2003,11 +2124,11 @@
       </c>
       <c r="F11">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G11">
         <f t="shared" si="7"/>
-        <v>470</v>
+        <v>630</v>
       </c>
       <c r="H11">
         <v>40</v>
@@ -2046,6 +2167,18 @@
         <v>40</v>
       </c>
       <c r="T11">
+        <v>40</v>
+      </c>
+      <c r="U11">
+        <v>40</v>
+      </c>
+      <c r="V11">
+        <v>40</v>
+      </c>
+      <c r="W11">
+        <v>40</v>
+      </c>
+      <c r="X11">
         <v>40</v>
       </c>
     </row>
@@ -2058,7 +2191,7 @@
       </c>
       <c r="C12" s="4">
         <f t="shared" si="3"/>
-        <v>68.174603174603178</v>
+        <v>70.714285714285708</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="4"/>
@@ -2074,7 +2207,7 @@
       </c>
       <c r="G12">
         <f t="shared" si="7"/>
-        <v>515</v>
+        <v>675</v>
       </c>
       <c r="H12">
         <v>40</v>
@@ -2113,6 +2246,18 @@
         <v>40</v>
       </c>
       <c r="T12">
+        <v>40</v>
+      </c>
+      <c r="U12">
+        <v>40</v>
+      </c>
+      <c r="V12">
+        <v>40</v>
+      </c>
+      <c r="W12">
+        <v>40</v>
+      </c>
+      <c r="X12">
         <v>40</v>
       </c>
     </row>
@@ -2125,7 +2270,7 @@
       </c>
       <c r="C13" s="4">
         <f t="shared" si="3"/>
-        <v>67.460317460317455</v>
+        <v>70</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="4"/>
@@ -2137,11 +2282,11 @@
       </c>
       <c r="F13">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G13">
         <f t="shared" si="7"/>
-        <v>470</v>
+        <v>630</v>
       </c>
       <c r="H13">
         <v>40</v>
@@ -2180,6 +2325,18 @@
         <v>40</v>
       </c>
       <c r="T13">
+        <v>40</v>
+      </c>
+      <c r="U13">
+        <v>40</v>
+      </c>
+      <c r="V13">
+        <v>40</v>
+      </c>
+      <c r="W13">
+        <v>40</v>
+      </c>
+      <c r="X13">
         <v>40</v>
       </c>
     </row>
@@ -2192,7 +2349,7 @@
       </c>
       <c r="C14" s="4">
         <f t="shared" si="3"/>
-        <v>68.031746031746025</v>
+        <v>70.571428571428569</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="4"/>
@@ -2208,7 +2365,7 @@
       </c>
       <c r="G14">
         <f t="shared" si="7"/>
-        <v>506</v>
+        <v>666</v>
       </c>
       <c r="H14">
         <v>40</v>
@@ -2247,6 +2404,18 @@
         <v>40</v>
       </c>
       <c r="T14">
+        <v>40</v>
+      </c>
+      <c r="U14">
+        <v>40</v>
+      </c>
+      <c r="V14">
+        <v>40</v>
+      </c>
+      <c r="W14">
+        <v>40</v>
+      </c>
+      <c r="X14">
         <v>40</v>
       </c>
     </row>
@@ -2259,7 +2428,7 @@
       </c>
       <c r="C15" s="4">
         <f t="shared" si="3"/>
-        <v>68.063492063492063</v>
+        <v>70.603174603174608</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="4"/>
@@ -2275,7 +2444,7 @@
       </c>
       <c r="G15">
         <f t="shared" si="7"/>
-        <v>508</v>
+        <v>668</v>
       </c>
       <c r="H15">
         <v>40</v>
@@ -2316,84 +2485,32 @@
       <c r="T15">
         <v>40</v>
       </c>
+      <c r="U15">
+        <v>40</v>
+      </c>
+      <c r="V15">
+        <v>40</v>
+      </c>
+      <c r="W15">
+        <v>40</v>
+      </c>
+      <c r="X15">
+        <v>40</v>
+      </c>
     </row>
     <row r="16" spans="1:195" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>14</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="4">
-        <f t="shared" si="3"/>
-        <v>67.761904761904759</v>
-      </c>
-      <c r="D16" s="4">
-        <f t="shared" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="E16" s="4">
-        <f t="shared" si="5"/>
-        <v>60</v>
-      </c>
-      <c r="F16">
-        <f t="shared" si="6"/>
-        <v>25</v>
-      </c>
-      <c r="G16">
-        <f t="shared" si="7"/>
-        <v>489</v>
-      </c>
-      <c r="H16">
-        <v>40</v>
-      </c>
-      <c r="I16">
-        <v>29</v>
-      </c>
-      <c r="J16">
-        <v>40</v>
-      </c>
-      <c r="K16">
-        <v>40</v>
-      </c>
-      <c r="L16">
-        <v>20</v>
-      </c>
-      <c r="M16">
-        <v>40</v>
-      </c>
-      <c r="N16">
-        <v>40</v>
-      </c>
-      <c r="O16">
-        <v>40</v>
-      </c>
-      <c r="P16">
-        <v>40</v>
-      </c>
-      <c r="Q16">
-        <v>40</v>
-      </c>
-      <c r="R16">
-        <v>40</v>
-      </c>
-      <c r="S16">
-        <v>40</v>
-      </c>
-      <c r="T16">
-        <v>40</v>
-      </c>
+      <c r="B16" s="5"/>
     </row>
     <row r="17" spans="1:219" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" s="4">
         <f t="shared" si="3"/>
-        <v>67.301587301587304</v>
+        <v>69.841269841269849</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="4"/>
@@ -2405,11 +2522,11 @@
       </c>
       <c r="F17">
         <f t="shared" si="6"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G17">
         <f t="shared" si="7"/>
-        <v>460</v>
+        <v>620</v>
       </c>
       <c r="H17">
         <v>40</v>
@@ -2448,6 +2565,18 @@
         <v>40</v>
       </c>
       <c r="T17">
+        <v>40</v>
+      </c>
+      <c r="U17">
+        <v>40</v>
+      </c>
+      <c r="V17">
+        <v>40</v>
+      </c>
+      <c r="W17">
+        <v>40</v>
+      </c>
+      <c r="X17">
         <v>40</v>
       </c>
     </row>
@@ -2456,11 +2585,11 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="3"/>
-        <v>67.777777777777771</v>
+        <v>70.317460317460316</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="4"/>
@@ -2476,7 +2605,7 @@
       </c>
       <c r="G18">
         <f t="shared" si="7"/>
-        <v>490</v>
+        <v>650</v>
       </c>
       <c r="H18">
         <v>40</v>
@@ -2515,6 +2644,18 @@
         <v>40</v>
       </c>
       <c r="T18">
+        <v>40</v>
+      </c>
+      <c r="U18">
+        <v>40</v>
+      </c>
+      <c r="V18">
+        <v>40</v>
+      </c>
+      <c r="W18">
+        <v>40</v>
+      </c>
+      <c r="X18">
         <v>40</v>
       </c>
     </row>
@@ -2523,11 +2664,11 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="3"/>
-        <v>67.460317460317455</v>
+        <v>70</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="4"/>
@@ -2539,11 +2680,11 @@
       </c>
       <c r="F19">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G19">
         <f t="shared" si="7"/>
-        <v>470</v>
+        <v>630</v>
       </c>
       <c r="H19">
         <v>40</v>
@@ -2582,6 +2723,18 @@
         <v>40</v>
       </c>
       <c r="T19">
+        <v>40</v>
+      </c>
+      <c r="U19">
+        <v>40</v>
+      </c>
+      <c r="V19">
+        <v>40</v>
+      </c>
+      <c r="W19">
+        <v>40</v>
+      </c>
+      <c r="X19">
         <v>40</v>
       </c>
     </row>
@@ -2590,11 +2743,11 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="3"/>
-        <v>68.238095238095241</v>
+        <v>70.777777777777771</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="4"/>
@@ -2610,7 +2763,7 @@
       </c>
       <c r="G20">
         <f t="shared" si="7"/>
-        <v>519</v>
+        <v>679</v>
       </c>
       <c r="H20">
         <v>40</v>
@@ -2649,6 +2802,18 @@
         <v>40</v>
       </c>
       <c r="T20">
+        <v>40</v>
+      </c>
+      <c r="U20">
+        <v>40</v>
+      </c>
+      <c r="V20">
+        <v>40</v>
+      </c>
+      <c r="W20">
+        <v>40</v>
+      </c>
+      <c r="X20">
         <v>40</v>
       </c>
     </row>
@@ -2657,11 +2822,11 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C21" s="4">
         <f t="shared" si="3"/>
-        <v>67.142857142857139</v>
+        <v>69.682539682539684</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="4"/>
@@ -2673,11 +2838,11 @@
       </c>
       <c r="F21">
         <f t="shared" si="6"/>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G21">
         <f t="shared" si="7"/>
-        <v>450</v>
+        <v>610</v>
       </c>
       <c r="H21">
         <v>40</v>
@@ -2716,6 +2881,18 @@
         <v>40</v>
       </c>
       <c r="T21">
+        <v>40</v>
+      </c>
+      <c r="U21">
+        <v>40</v>
+      </c>
+      <c r="V21">
+        <v>40</v>
+      </c>
+      <c r="W21">
+        <v>40</v>
+      </c>
+      <c r="X21">
         <v>40</v>
       </c>
     </row>
@@ -2724,11 +2901,11 @@
         <v>20</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" si="3"/>
-        <v>68.111111111111114</v>
+        <v>70.650793650793645</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="4"/>
@@ -2744,7 +2921,7 @@
       </c>
       <c r="G22">
         <f t="shared" si="7"/>
-        <v>511</v>
+        <v>671</v>
       </c>
       <c r="H22">
         <v>40</v>
@@ -2785,10 +2962,18 @@
       <c r="T22">
         <v>40</v>
       </c>
-      <c r="U22"/>
-      <c r="V22"/>
-      <c r="W22"/>
-      <c r="X22"/>
+      <c r="U22">
+        <v>40</v>
+      </c>
+      <c r="V22">
+        <v>40</v>
+      </c>
+      <c r="W22">
+        <v>40</v>
+      </c>
+      <c r="X22">
+        <v>40</v>
+      </c>
       <c r="Y22"/>
       <c r="Z22"/>
       <c r="AA22"/>
@@ -2990,11 +3175,11 @@
         <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23" s="4">
         <f t="shared" ref="C23:C36" si="8">SUM(H23:BR23)/63+60</f>
-        <v>67.952380952380949</v>
+        <v>70.492063492063494</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" ref="D23:D36" si="9">SUM(BS23:EH23)/(131-63)+60</f>
@@ -3010,7 +3195,7 @@
       </c>
       <c r="G23">
         <f t="shared" si="7"/>
-        <v>501</v>
+        <v>661</v>
       </c>
       <c r="H23">
         <v>40</v>
@@ -3049,6 +3234,18 @@
         <v>40</v>
       </c>
       <c r="T23">
+        <v>40</v>
+      </c>
+      <c r="U23">
+        <v>40</v>
+      </c>
+      <c r="V23">
+        <v>40</v>
+      </c>
+      <c r="W23">
+        <v>40</v>
+      </c>
+      <c r="X23">
         <v>40</v>
       </c>
     </row>
@@ -3057,11 +3254,11 @@
         <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="8"/>
-        <v>67.777777777777771</v>
+        <v>70.317460317460316</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="9"/>
@@ -3077,7 +3274,7 @@
       </c>
       <c r="G24">
         <f t="shared" si="7"/>
-        <v>490</v>
+        <v>650</v>
       </c>
       <c r="H24">
         <v>40</v>
@@ -3116,6 +3313,18 @@
         <v>40</v>
       </c>
       <c r="T24">
+        <v>40</v>
+      </c>
+      <c r="U24">
+        <v>40</v>
+      </c>
+      <c r="V24">
+        <v>40</v>
+      </c>
+      <c r="W24">
+        <v>40</v>
+      </c>
+      <c r="X24">
         <v>40</v>
       </c>
     </row>
@@ -3124,11 +3333,11 @@
         <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C25" s="4">
         <f t="shared" si="8"/>
-        <v>67.777777777777771</v>
+        <v>70.317460317460316</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="9"/>
@@ -3144,7 +3353,7 @@
       </c>
       <c r="G25">
         <f t="shared" si="7"/>
-        <v>490</v>
+        <v>650</v>
       </c>
       <c r="H25">
         <v>40</v>
@@ -3183,6 +3392,18 @@
         <v>40</v>
       </c>
       <c r="T25">
+        <v>40</v>
+      </c>
+      <c r="U25">
+        <v>40</v>
+      </c>
+      <c r="V25">
+        <v>40</v>
+      </c>
+      <c r="W25">
+        <v>40</v>
+      </c>
+      <c r="X25">
         <v>40</v>
       </c>
     </row>
@@ -3191,11 +3412,11 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="8"/>
-        <v>67.936507936507937</v>
+        <v>70.476190476190482</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="9"/>
@@ -3211,7 +3432,7 @@
       </c>
       <c r="G26">
         <f t="shared" si="7"/>
-        <v>500</v>
+        <v>660</v>
       </c>
       <c r="H26">
         <v>40</v>
@@ -3250,6 +3471,18 @@
         <v>40</v>
       </c>
       <c r="T26">
+        <v>40</v>
+      </c>
+      <c r="U26">
+        <v>40</v>
+      </c>
+      <c r="V26">
+        <v>40</v>
+      </c>
+      <c r="W26">
+        <v>40</v>
+      </c>
+      <c r="X26">
         <v>40</v>
       </c>
     </row>
@@ -3258,11 +3491,11 @@
         <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" si="8"/>
-        <v>68.253968253968253</v>
+        <v>70.793650793650798</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="9"/>
@@ -3278,7 +3511,7 @@
       </c>
       <c r="G27">
         <f t="shared" si="7"/>
-        <v>520</v>
+        <v>680</v>
       </c>
       <c r="H27">
         <v>40</v>
@@ -3317,6 +3550,18 @@
         <v>40</v>
       </c>
       <c r="T27">
+        <v>40</v>
+      </c>
+      <c r="U27">
+        <v>40</v>
+      </c>
+      <c r="V27">
+        <v>40</v>
+      </c>
+      <c r="W27">
+        <v>40</v>
+      </c>
+      <c r="X27">
         <v>40</v>
       </c>
     </row>
@@ -3325,11 +3570,11 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C28" s="4">
         <f t="shared" si="8"/>
-        <v>67.777777777777771</v>
+        <v>70.317460317460316</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="9"/>
@@ -3345,7 +3590,7 @@
       </c>
       <c r="G28">
         <f t="shared" si="7"/>
-        <v>490</v>
+        <v>650</v>
       </c>
       <c r="H28">
         <v>40</v>
@@ -3384,6 +3629,18 @@
         <v>40</v>
       </c>
       <c r="T28">
+        <v>40</v>
+      </c>
+      <c r="U28">
+        <v>40</v>
+      </c>
+      <c r="V28">
+        <v>40</v>
+      </c>
+      <c r="W28">
+        <v>40</v>
+      </c>
+      <c r="X28">
         <v>40</v>
       </c>
     </row>
@@ -3392,11 +3649,11 @@
         <v>27</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29" s="4">
         <f t="shared" si="8"/>
-        <v>68.015873015873012</v>
+        <v>70.555555555555557</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="9"/>
@@ -3412,7 +3669,7 @@
       </c>
       <c r="G29">
         <f t="shared" si="7"/>
-        <v>505</v>
+        <v>665</v>
       </c>
       <c r="H29">
         <v>40</v>
@@ -3451,6 +3708,18 @@
         <v>40</v>
       </c>
       <c r="T29">
+        <v>40</v>
+      </c>
+      <c r="U29">
+        <v>40</v>
+      </c>
+      <c r="V29">
+        <v>40</v>
+      </c>
+      <c r="W29">
+        <v>40</v>
+      </c>
+      <c r="X29">
         <v>40</v>
       </c>
     </row>
@@ -3459,11 +3728,11 @@
         <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C30" s="4">
         <f t="shared" si="8"/>
-        <v>67.682539682539684</v>
+        <v>70.222222222222229</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="9"/>
@@ -3475,11 +3744,11 @@
       </c>
       <c r="F30">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G30">
         <f t="shared" si="7"/>
-        <v>484</v>
+        <v>644</v>
       </c>
       <c r="H30">
         <v>40</v>
@@ -3518,6 +3787,18 @@
         <v>40</v>
       </c>
       <c r="T30">
+        <v>40</v>
+      </c>
+      <c r="U30">
+        <v>40</v>
+      </c>
+      <c r="V30">
+        <v>40</v>
+      </c>
+      <c r="W30">
+        <v>40</v>
+      </c>
+      <c r="X30">
         <v>40</v>
       </c>
     </row>
@@ -3526,11 +3807,11 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C31" s="4">
         <f t="shared" si="8"/>
-        <v>68.031746031746025</v>
+        <v>70.571428571428569</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="9"/>
@@ -3546,7 +3827,7 @@
       </c>
       <c r="G31">
         <f t="shared" si="7"/>
-        <v>506</v>
+        <v>666</v>
       </c>
       <c r="H31">
         <v>40</v>
@@ -3585,6 +3866,18 @@
         <v>40</v>
       </c>
       <c r="T31">
+        <v>40</v>
+      </c>
+      <c r="U31">
+        <v>40</v>
+      </c>
+      <c r="V31">
+        <v>40</v>
+      </c>
+      <c r="W31">
+        <v>40</v>
+      </c>
+      <c r="X31">
         <v>40</v>
       </c>
     </row>
@@ -3593,11 +3886,11 @@
         <v>30</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C32" s="4">
         <f t="shared" si="8"/>
-        <v>68.158730158730151</v>
+        <v>70.698412698412696</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="9"/>
@@ -3613,7 +3906,7 @@
       </c>
       <c r="G32">
         <f t="shared" si="7"/>
-        <v>514</v>
+        <v>674</v>
       </c>
       <c r="H32">
         <v>40</v>
@@ -3652,6 +3945,18 @@
         <v>40</v>
       </c>
       <c r="T32">
+        <v>40</v>
+      </c>
+      <c r="U32">
+        <v>40</v>
+      </c>
+      <c r="V32">
+        <v>40</v>
+      </c>
+      <c r="W32">
+        <v>40</v>
+      </c>
+      <c r="X32">
         <v>40</v>
       </c>
     </row>
@@ -3660,11 +3965,11 @@
         <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C33" s="4">
         <f t="shared" si="8"/>
-        <v>68.047619047619051</v>
+        <v>70.587301587301582</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" si="9"/>
@@ -3680,7 +3985,7 @@
       </c>
       <c r="G33">
         <f t="shared" si="7"/>
-        <v>507</v>
+        <v>667</v>
       </c>
       <c r="H33">
         <v>40</v>
@@ -3719,6 +4024,18 @@
         <v>40</v>
       </c>
       <c r="T33">
+        <v>40</v>
+      </c>
+      <c r="U33">
+        <v>40</v>
+      </c>
+      <c r="V33">
+        <v>40</v>
+      </c>
+      <c r="W33">
+        <v>40</v>
+      </c>
+      <c r="X33">
         <v>40</v>
       </c>
     </row>
@@ -3727,11 +4044,11 @@
         <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C34" s="4">
         <f t="shared" si="8"/>
-        <v>68.126984126984127</v>
+        <v>70.666666666666671</v>
       </c>
       <c r="D34" s="4">
         <f t="shared" si="9"/>
@@ -3747,7 +4064,7 @@
       </c>
       <c r="G34">
         <f t="shared" si="7"/>
-        <v>512</v>
+        <v>672</v>
       </c>
       <c r="H34">
         <v>40</v>
@@ -3786,6 +4103,18 @@
         <v>40</v>
       </c>
       <c r="T34">
+        <v>40</v>
+      </c>
+      <c r="U34">
+        <v>40</v>
+      </c>
+      <c r="V34">
+        <v>40</v>
+      </c>
+      <c r="W34">
+        <v>40</v>
+      </c>
+      <c r="X34">
         <v>40</v>
       </c>
     </row>
@@ -3794,11 +4123,11 @@
         <v>33</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C35" s="4">
         <f t="shared" si="8"/>
-        <v>68.206349206349202</v>
+        <v>70.746031746031747</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="9"/>
@@ -3814,7 +4143,7 @@
       </c>
       <c r="G35">
         <f t="shared" si="7"/>
-        <v>517</v>
+        <v>677</v>
       </c>
       <c r="H35">
         <v>40</v>
@@ -3853,6 +4182,18 @@
         <v>40</v>
       </c>
       <c r="T35">
+        <v>40</v>
+      </c>
+      <c r="U35">
+        <v>40</v>
+      </c>
+      <c r="V35">
+        <v>40</v>
+      </c>
+      <c r="W35">
+        <v>40</v>
+      </c>
+      <c r="X35">
         <v>40</v>
       </c>
     </row>
@@ -3861,11 +4202,11 @@
         <v>34</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C36" s="4">
         <f t="shared" si="8"/>
-        <v>67.777777777777771</v>
+        <v>70.317460317460316</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="9"/>
@@ -3881,7 +4222,7 @@
       </c>
       <c r="G36">
         <f t="shared" si="7"/>
-        <v>490</v>
+        <v>650</v>
       </c>
       <c r="H36">
         <v>40</v>
@@ -3920,6 +4261,18 @@
         <v>40</v>
       </c>
       <c r="T36">
+        <v>40</v>
+      </c>
+      <c r="U36">
+        <v>40</v>
+      </c>
+      <c r="V36">
+        <v>40</v>
+      </c>
+      <c r="W36">
+        <v>40</v>
+      </c>
+      <c r="X36">
         <v>40</v>
       </c>
     </row>
@@ -4565,7 +4918,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:I36 J3:QB3 U4:QB21 J4:T36">
+  <conditionalFormatting sqref="H3:I36 Y4:QB21 J3:QB3 J4:X36">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
